--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Equity Savings Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Equity Savings Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="337">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Equity Savings Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,6 +61,15 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>Reliance Industries Ltd.</t>
   </si>
   <si>
@@ -70,15 +79,6 @@
     <t>Petroleum Products</t>
   </si>
   <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
   </si>
   <si>
@@ -97,6 +97,57 @@
     <t>Diversified Fmcg</t>
   </si>
   <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE155A01022</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
     <t>HDFC Life Insurance Company Ltd.</t>
   </si>
   <si>
@@ -106,22 +157,70 @@
     <t>Insurance</t>
   </si>
   <si>
-    <t>Tata Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE155A01022</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
+    <t>Kotak Mahindra Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE237A01028</t>
+  </si>
+  <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Bajaj Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE296A01024</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd.</t>
+  </si>
+  <si>
+    <t>INE158A01026</t>
+  </si>
+  <si>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
   </si>
   <si>
     <t>Cipla Ltd.</t>
@@ -130,70 +229,31 @@
     <t>INE059A01026</t>
   </si>
   <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Adani Ports and Special Economic Zone Ltd.</t>
-  </si>
-  <si>
-    <t>INE742F01042</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Hero Motocorp Ltd.</t>
-  </si>
-  <si>
-    <t>INE158A01026</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE467B01029</t>
-  </si>
-  <si>
-    <t>Bajaj Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE296A01024</t>
-  </si>
-  <si>
-    <t>Finance</t>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>ITC Ltd.</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
   </si>
   <si>
     <t>HCL Technologies Ltd.</t>
@@ -202,37 +262,22 @@
     <t>INE860A01027</t>
   </si>
   <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Nestle India Ltd.</t>
+  </si>
+  <si>
+    <t>INE239A01024</t>
+  </si>
+  <si>
+    <t>Food Products</t>
   </si>
   <si>
     <t>Wipro Ltd.</t>
@@ -241,10 +286,61 @@
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
+    <t>Power Grid Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE752E01010</t>
+  </si>
+  <si>
+    <t>Bajaj Finserv Ltd.</t>
+  </si>
+  <si>
+    <t>INE918I01026</t>
+  </si>
+  <si>
+    <t>Sagility India Ltd</t>
+  </si>
+  <si>
+    <t>INE0W2G01015</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>Cigniti Technologies Ltd</t>
+  </si>
+  <si>
+    <t>INE675C01017</t>
+  </si>
+  <si>
+    <t>Coal India Ltd.</t>
+  </si>
+  <si>
+    <t>INE522F01014</t>
+  </si>
+  <si>
+    <t>Consumable Fuels</t>
+  </si>
+  <si>
+    <t>Vodafone Idea Ltd.</t>
+  </si>
+  <si>
+    <t>INE669E01016</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>JSW Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE019A01038</t>
   </si>
   <si>
     <t>Maruti Suzuki India Ltd.</t>
@@ -253,79 +349,193 @@
     <t>INE585B01010</t>
   </si>
   <si>
-    <t>Nestle India Ltd.</t>
-  </si>
-  <si>
-    <t>INE239A01024</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE237A01028</t>
-  </si>
-  <si>
-    <t>Power Grid Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE752E01010</t>
-  </si>
-  <si>
-    <t>Vodafone Idea Ltd.</t>
-  </si>
-  <si>
-    <t>INE669E01016</t>
-  </si>
-  <si>
-    <t>Coal India Ltd.</t>
-  </si>
-  <si>
-    <t>INE522F01014</t>
-  </si>
-  <si>
-    <t>Consumable Fuels</t>
-  </si>
-  <si>
-    <t>Cigniti Technologies Ltd</t>
-  </si>
-  <si>
-    <t>INE675C01017</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>Bajaj Finserv Ltd.</t>
-  </si>
-  <si>
-    <t>INE918I01026</t>
-  </si>
-  <si>
-    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE213A01029</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>ITC Ltd.</t>
-  </si>
-  <si>
-    <t>INE154A01025</t>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A01022</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>Titan Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE280A01028</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>GAIL (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE129A01019</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Indus Towers Ltd.</t>
+  </si>
+  <si>
+    <t>INE121J01017</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Punjab National Bank</t>
+  </si>
+  <si>
+    <t>INE160A01022</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Jindal Steel &amp; Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE749A01030</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Bharat Electronics Ltd.</t>
+  </si>
+  <si>
+    <t>INE263A01024</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Hindustan Aeronautics Ltd.</t>
+  </si>
+  <si>
+    <t>INE066F01020</t>
+  </si>
+  <si>
+    <t>Eicher Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE066A01021</t>
+  </si>
+  <si>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>LTIMindtree Ltd.</t>
+  </si>
+  <si>
+    <t>INE214T01019</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Tata Power Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>Apollo Hospitals Enterprise Ltd.</t>
+  </si>
+  <si>
+    <t>INE437A01024</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>United Spirits Ltd.</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE115A01026</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda</t>
+  </si>
+  <si>
+    <t>INE028A01039</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
   </si>
   <si>
     <t>Adani Wilmar Ltd</t>
@@ -337,237 +547,69 @@
     <t>Agricultural Food &amp; Other Products</t>
   </si>
   <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
-  </si>
-  <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A01022</t>
-  </si>
-  <si>
-    <t>Titan Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE280A01028</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE242A01010</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>GAIL (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE129A01019</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>UPL Ltd. (Right Share)</t>
-  </si>
-  <si>
-    <t>IN9628A01018</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Indus Towers Ltd.</t>
-  </si>
-  <si>
-    <t>INE121J01017</t>
-  </si>
-  <si>
-    <t>LTIMindtree Ltd.</t>
-  </si>
-  <si>
-    <t>INE214T01019</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A01022</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Eicher Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE066A01021</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>Tata Power Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE245A01021</t>
-  </si>
-  <si>
-    <t>Apollo Hospitals Enterprise Ltd.</t>
-  </si>
-  <si>
-    <t>INE437A01024</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>United Spirits Ltd.</t>
-  </si>
-  <si>
-    <t>INE854D01024</t>
-  </si>
-  <si>
-    <t>Beverages</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A01039</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd. (Covered call) $$</t>
+    <t>Container Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE111A01025</t>
   </si>
   <si>
     <t>^</t>
   </si>
   <si>
+    <t>Hindustan Unilever Ltd. (Covered call) $$</t>
+  </si>
+  <si>
     <t>Nestle India Ltd. (Covered call) $$</t>
   </si>
   <si>
+    <t>Infosys Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki India Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Cipla Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Wipro Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>ITC Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd. (Covered call) $$</t>
+  </si>
+  <si>
     <t>ICICI Bank Ltd. (Covered call) $$</t>
   </si>
   <si>
-    <t>ITC Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Dr. Reddy's Laboratories Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Wipro Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services Ltd. (Covered call) $$</t>
+    <t>Mahindra &amp; Mahindra Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>NTPC Ltd. (Covered call) $$</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd. (Covered call) $$</t>
   </si>
   <si>
     <t>State Bank Of India (Covered call) $$</t>
   </si>
   <si>
-    <t>Hero Motocorp Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Hindustan Unilever Ltd. (Covered call) $$</t>
-  </si>
-  <si>
     <t>Axis Bank Ltd. (Covered call) $$</t>
   </si>
   <si>
-    <t>Infosys Ltd. (Covered call) $$</t>
-  </si>
-  <si>
-    <t>Cipla Ltd. (Covered call) $$</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -580,7 +622,7 @@
     <t>Government Securities</t>
   </si>
   <si>
-    <t>IN0020230085</t>
+    <t>IN0020240126</t>
   </si>
   <si>
     <t>SOV</t>
@@ -589,12 +631,30 @@
     <t>IN0020240019</t>
   </si>
   <si>
-    <t>IN0020230010</t>
-  </si>
-  <si>
     <t>IN0020210137</t>
   </si>
   <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
+  </si>
+  <si>
     <t>IN0020220151</t>
   </si>
   <si>
@@ -610,6 +670,15 @@
     <t>CRISIL AA+</t>
   </si>
   <si>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A07RF8</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
     <t>Godrej Industries Ltd. **</t>
   </si>
   <si>
@@ -622,15 +691,6 @@
     <t>INE721A07RR8</t>
   </si>
   <si>
-    <t>NTPC Ltd. **</t>
-  </si>
-  <si>
-    <t>INE733E07JP6</t>
-  </si>
-  <si>
-    <t>CRISIL AAA</t>
-  </si>
-  <si>
     <t>Zero Coupon Bonds / Deep Discount Bonds</t>
   </si>
   <si>
@@ -643,18 +703,18 @@
     <t>India Universal Trust AL2 **</t>
   </si>
   <si>
+    <t>INE1CBK15037</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(SO)</t>
+  </si>
+  <si>
+    <t>INE1CBK15029</t>
+  </si>
+  <si>
     <t>INE1CBK15011</t>
   </si>
   <si>
-    <t>CRISIL AAA(SO)</t>
-  </si>
-  <si>
-    <t>INE1CBK15029</t>
-  </si>
-  <si>
-    <t>INE1CBK15037</t>
-  </si>
-  <si>
     <t>Term Deposits</t>
   </si>
   <si>
@@ -685,13 +745,13 @@
     <t>INE238AD6AE9</t>
   </si>
   <si>
-    <t>INE160A16PK9</t>
-  </si>
-  <si>
-    <t>Indian Bank **</t>
-  </si>
-  <si>
-    <t>INE562A16MZ1</t>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F16975</t>
+  </si>
+  <si>
+    <t>INE556F16BD2</t>
   </si>
   <si>
     <t>Commercial Papers</t>
@@ -712,9 +772,6 @@
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>Reverse Repo</t>
-  </si>
-  <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
   </si>
   <si>
@@ -754,16 +811,22 @@
     <t>Stock / Index Futures</t>
   </si>
   <si>
+    <t>Container Corporation of India Ltd. $$</t>
+  </si>
+  <si>
     <t>TVS Motor Company Ltd. $$</t>
   </si>
   <si>
     <t>Bank Of Baroda $$</t>
   </si>
   <si>
+    <t>LIC Housing Finance Ltd. $$</t>
+  </si>
+  <si>
     <t>United Spirits Ltd. $$</t>
   </si>
   <si>
-    <t>Samvardhana Motherson International Ltd. $$</t>
+    <t>Motherson Sumi Systems Ltd. $$</t>
   </si>
   <si>
     <t>Apollo Hospitals Enterprise Ltd. $$</t>
@@ -775,144 +838,144 @@
     <t>ICICI Lombard General Insurance Company Ltd. $$</t>
   </si>
   <si>
+    <t>LTIMindtree Ltd. $$</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd. $$</t>
+  </si>
+  <si>
     <t>Grasim Industries Ltd. $$</t>
   </si>
   <si>
     <t>Eicher Motors Ltd. $$</t>
   </si>
   <si>
+    <t>Hindustan Aeronautics Ltd. $$</t>
+  </si>
+  <si>
+    <t>Bharat Electronics Ltd. $$</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd. $$</t>
+  </si>
+  <si>
     <t>IndusInd Bank Ltd. $$</t>
   </si>
   <si>
+    <t>Tata Consultancy Services Ltd. $$</t>
+  </si>
+  <si>
+    <t>Jindal Steel &amp; Power Ltd. $$</t>
+  </si>
+  <si>
+    <t>Hero Motocorp Ltd. $$</t>
+  </si>
+  <si>
+    <t>Lupin Ltd. $$</t>
+  </si>
+  <si>
+    <t>Punjab National Bank $$</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd. $$</t>
+  </si>
+  <si>
+    <t>Indus Towers Ltd. $$</t>
+  </si>
+  <si>
+    <t>GAIL (India) Ltd. $$</t>
+  </si>
+  <si>
+    <t>Titan Company Ltd. $$</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd. $$</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd. $$</t>
+  </si>
+  <si>
     <t>Britannia Industries Ltd. $$</t>
   </si>
   <si>
-    <t>Syngene International Ltd. $$</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd. $$</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd. $$</t>
-  </si>
-  <si>
-    <t>Punjab National Bank $$</t>
-  </si>
-  <si>
-    <t>LTIMindtree Ltd. $$</t>
-  </si>
-  <si>
-    <t>Nestle India Ltd. $$</t>
-  </si>
-  <si>
-    <t>Indus Towers Ltd. $$</t>
-  </si>
-  <si>
     <t>Ultratech Cement Ltd. $$</t>
   </si>
   <si>
-    <t>GAIL (India) Ltd. $$</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd. $$</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd. $$</t>
-  </si>
-  <si>
-    <t>State Bank Of India $$</t>
-  </si>
-  <si>
-    <t>Titan Company Ltd. $$</t>
-  </si>
-  <si>
     <t>Canara Bank $$</t>
   </si>
   <si>
     <t>JSW Steel Ltd. $$</t>
   </si>
   <si>
-    <t>Hero Motocorp Ltd. $$</t>
-  </si>
-  <si>
     <t>Oil &amp; Natural Gas Corporation Ltd. $$</t>
   </si>
   <si>
+    <t>Vodafone Idea Ltd. $$</t>
+  </si>
+  <si>
+    <t>Coal India Ltd. $$</t>
+  </si>
+  <si>
     <t>Bajaj Finserv Ltd. $$</t>
   </si>
   <si>
-    <t>Coal India Ltd. $$</t>
-  </si>
-  <si>
-    <t>Wipro Ltd. $$</t>
-  </si>
-  <si>
     <t>Power Grid Corporation Of India Ltd. $$</t>
   </si>
   <si>
-    <t>Vodafone Idea Ltd. $$</t>
+    <t>Infosys Ltd. $$</t>
   </si>
   <si>
     <t>Axis Bank Ltd. $$</t>
   </si>
   <si>
+    <t>Bharti Airtel Ltd. $$</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd. $$</t>
+  </si>
+  <si>
+    <t>ICICI Bank Ltd. $$</t>
+  </si>
+  <si>
+    <t>Cipla Ltd. $$</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd. $$</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd. $$</t>
+  </si>
+  <si>
+    <t>Larsen &amp; Toubro Ltd. $$</t>
+  </si>
+  <si>
+    <t>Hindustan Unilever Ltd. $$</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd. $$</t>
+  </si>
+  <si>
+    <t>Bajaj Finance Ltd. $$</t>
+  </si>
+  <si>
     <t>Kotak Mahindra Bank Ltd. $$</t>
   </si>
   <si>
-    <t>Tata Consultancy Services Ltd. $$</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd. $$</t>
-  </si>
-  <si>
-    <t>Maruti Suzuki India Ltd. $$</t>
+    <t>HDFC Life Insurance Company Ltd $$</t>
   </si>
   <si>
     <t>Ambuja Cements Ltd. $$</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd. $$</t>
-  </si>
-  <si>
-    <t>Cipla Ltd. $$</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd. $$</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd. $$</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd. $$</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd. $$</t>
-  </si>
-  <si>
-    <t>Infosys Ltd. $$</t>
-  </si>
-  <si>
-    <t>Bajaj Finance Ltd. $$</t>
-  </si>
-  <si>
-    <t>Hindustan Unilever Ltd. $$</t>
-  </si>
-  <si>
-    <t>HDFC Life Insurance Company Ltd $$</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd. $$</t>
+    <t>NTPC Ltd. $$</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd. $$</t>
   </si>
   <si>
     <t>Adani Ports and Special Economic Zone Ltd. $$</t>
   </si>
   <si>
-    <t>Tata Motors Ltd. $$</t>
-  </si>
-  <si>
-    <t>NTPC Ltd. $$</t>
-  </si>
-  <si>
     <t>Sun Pharmaceutical Industries Ltd. $$</t>
   </si>
   <si>
@@ -946,7 +1009,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1344,13 +1407,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>234</xdr:row>
+      <xdr:row>241</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>244</xdr:row>
+      <xdr:row>251</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1368,7 +1431,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="45596175"/>
+          <a:off x="666750" y="46767750"/>
           <a:ext cx="4533900" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1383,13 +1446,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>249</xdr:row>
+      <xdr:row>256</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>259</xdr:row>
+      <xdr:row>266</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1407,7 +1470,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="48453675"/>
+          <a:off x="666750" y="49625250"/>
           <a:ext cx="4533900" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1741,12 +1804,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J248"/>
+  <dimension ref="B1:J255"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="23" width="10.0" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="23" width="68.0" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="16.857142857142858" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="17.0" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="23" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="23" width="47.142857142857146" collapsed="true"/>
     <col min="6" max="6" bestFit="true" customWidth="true" style="23" width="13.285714285714286" collapsed="true"/>
@@ -1841,10 +1904,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>874040.7199999999</v>
+        <v>944676.8999999999</v>
       </c>
       <c r="H5" s="10">
-        <v>0.6834591549135001</v>
+        <v>0.6969092779154</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1878,10 +1941,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>874040.7199999999</v>
+        <v>944676.8999999999</v>
       </c>
       <c r="H7" s="10">
-        <v>0.6834591549135001</v>
+        <v>0.6969092779154</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1904,13 +1967,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>7418569</v>
+        <v>5701058</v>
       </c>
       <c r="G8" s="15">
-        <v>93852.32</v>
+        <v>110879.88</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0733881452503</v>
+        <v>0.0817985674323</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1933,13 +1996,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>4630458</v>
+        <v>5686903</v>
       </c>
       <c r="G9" s="15">
-        <v>78659.91</v>
+        <v>80805.20</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0615083878635</v>
+        <v>0.0596118033414</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1962,13 +2025,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>2907782</v>
+        <v>3544956</v>
       </c>
       <c r="G10" s="15">
-        <v>50710.26</v>
+        <v>59470.18</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0396530626686</v>
+        <v>0.0438724819051</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1991,13 +2054,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>1418004</v>
+        <v>1881680</v>
       </c>
       <c r="G11" s="15">
-        <v>35007.68</v>
+        <v>44187.49</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0273743760912</v>
+        <v>0.0325980996771</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -2020,13 +2083,13 @@
         <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>5250494</v>
+        <v>11298122</v>
       </c>
       <c r="G12" s="15">
-        <v>33500.78</v>
+        <v>37724.43</v>
       </c>
       <c r="H12" s="16">
-        <v>0.02619605044</v>
+        <v>0.0278301557613</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -2049,13 +2112,13 @@
         <v>32</v>
       </c>
       <c r="F13" s="14">
-        <v>4588847</v>
+        <v>2365600</v>
       </c>
       <c r="G13" s="15">
-        <v>32860.73</v>
+        <v>33894.32</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0256955611355</v>
+        <v>0.0250045979495</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -2078,13 +2141,13 @@
         <v>35</v>
       </c>
       <c r="F14" s="14">
-        <v>9597387</v>
+        <v>4474997</v>
       </c>
       <c r="G14" s="15">
-        <v>31095.53</v>
+        <v>32197.60</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0243152569086</v>
+        <v>0.0237528896564</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -2104,16 +2167,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F15" s="14">
-        <v>1917935</v>
+        <v>814624</v>
       </c>
       <c r="G15" s="15">
-        <v>28373.93</v>
+        <v>28213.69</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0221870924039</v>
+        <v>0.0208138701447</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -2124,25 +2187,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" s="14">
-        <v>1447242</v>
+        <v>5046743</v>
       </c>
       <c r="G16" s="15">
-        <v>27205.26</v>
+        <v>27933.72</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0212732468675</v>
+        <v>0.0206073300138</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -2153,25 +2216,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F17" s="14">
-        <v>2365600</v>
+        <v>858457</v>
       </c>
       <c r="G17" s="15">
-        <v>26006.22</v>
+        <v>25554.55</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0203356534049</v>
+        <v>0.0188521630919</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -2194,13 +2257,13 @@
         <v>46</v>
       </c>
       <c r="F18" s="14">
-        <v>5046743</v>
+        <v>3259300</v>
       </c>
       <c r="G18" s="15">
-        <v>25879.70</v>
+        <v>25319.87</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0202367206546</v>
+        <v>0.018679034407</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -2220,16 +2283,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F19" s="14">
-        <v>826000</v>
+        <v>1212000</v>
       </c>
       <c r="G19" s="15">
-        <v>24696.16</v>
+        <v>25145.36</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0193112474705</v>
+        <v>0.0185502944769</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2249,16 +2312,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20" s="14">
-        <v>2496213</v>
+        <v>1663500</v>
       </c>
       <c r="G20" s="15">
-        <v>24615.16</v>
+        <v>24050.88</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0192479092412</v>
+        <v>0.0177428721016</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2278,16 +2341,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="F21" s="14">
-        <v>1877000</v>
+        <v>253750</v>
       </c>
       <c r="G21" s="15">
-        <v>23515.06</v>
+        <v>23295.52</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0183876822528</v>
+        <v>0.0171856261351</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2298,25 +2361,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F22" s="14">
-        <v>475685</v>
+        <v>1784735</v>
       </c>
       <c r="G22" s="15">
-        <v>20640.69</v>
+        <v>21277.61</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0161400587197</v>
+        <v>0.0156969687952</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2327,25 +2390,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F23" s="14">
-        <v>490329</v>
+        <v>366671</v>
       </c>
       <c r="G23" s="15">
-        <v>20164.29</v>
+        <v>19543.56</v>
       </c>
       <c r="H23" s="16">
-        <v>0.015767536097</v>
+        <v>0.0144177213262</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2356,25 +2419,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F24" s="14">
-        <v>253750</v>
+        <v>520800</v>
       </c>
       <c r="G24" s="15">
-        <v>20008.44</v>
+        <v>19139.92</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0156456686521</v>
+        <v>0.0141199470703</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2385,25 +2448,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F25" s="14">
-        <v>1052650</v>
+        <v>11709500</v>
       </c>
       <c r="G25" s="15">
-        <v>18162.95</v>
+        <v>18854.64</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0142025813829</v>
+        <v>0.0139094896337</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2414,25 +2477,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F26" s="14">
-        <v>2172632</v>
+        <v>426685</v>
       </c>
       <c r="G26" s="15">
-        <v>16792.27</v>
+        <v>18387.14</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0131307734304</v>
+        <v>0.0135646044275</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2443,25 +2506,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="F27" s="14">
-        <v>3578800</v>
+        <v>1168966</v>
       </c>
       <c r="G27" s="15">
-        <v>15796.82</v>
+        <v>18267.43</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0123523778703</v>
+        <v>0.0134762916831</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2472,25 +2535,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F28" s="14">
-        <v>437100</v>
+        <v>1158410</v>
       </c>
       <c r="G28" s="15">
-        <v>15593.11</v>
+        <v>16978.82</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0121930861334</v>
+        <v>0.0125256552648</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2501,25 +2564,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F29" s="14">
-        <v>11412500</v>
+        <v>2028678</v>
       </c>
       <c r="G29" s="15">
-        <v>15363.51</v>
+        <v>16478.95</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0120135496217</v>
+        <v>0.0121568899857</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2539,16 +2602,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F30" s="14">
-        <v>4461019</v>
+        <v>3578800</v>
       </c>
       <c r="G30" s="15">
-        <v>13913.92</v>
+        <v>15587.46</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0108800377226</v>
+        <v>0.0114992178735</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2559,10 +2622,10 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
@@ -2571,13 +2634,13 @@
         <v>23</v>
       </c>
       <c r="F31" s="14">
-        <v>1086065</v>
+        <v>1187748</v>
       </c>
       <c r="G31" s="15">
-        <v>13221.21</v>
+        <v>14861.10</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0103383707495</v>
+        <v>0.0109633658556</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2588,25 +2651,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F32" s="14">
-        <v>107050</v>
+        <v>3391830</v>
       </c>
       <c r="G32" s="15">
-        <v>13178.55</v>
+        <v>14179.55</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0103050126154</v>
+        <v>0.0104605711769</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2617,25 +2680,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="F33" s="14">
-        <v>504367</v>
+        <v>817107</v>
       </c>
       <c r="G33" s="15">
-        <v>11667.02</v>
+        <v>13372.77</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0091230665198</v>
+        <v>0.0098653915264</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2658,13 +2721,13 @@
         <v>84</v>
       </c>
       <c r="F34" s="14">
-        <v>713925</v>
+        <v>712025</v>
       </c>
       <c r="G34" s="15">
-        <v>11610.56</v>
+        <v>13216.61</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0090789174281</v>
+        <v>0.0097501888017</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2684,16 +2747,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F35" s="14">
-        <v>562000</v>
+        <v>442167</v>
       </c>
       <c r="G35" s="15">
-        <v>10685.31</v>
+        <v>10595.21</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0083554150001</v>
+        <v>0.007816323391</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2704,25 +2767,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F36" s="14">
-        <v>3004200</v>
+        <v>4129989</v>
       </c>
       <c r="G36" s="15">
-        <v>9062.17</v>
+        <v>10311.34</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0070861950801</v>
+        <v>0.007606906143</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2733,25 +2796,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="F37" s="14">
-        <v>100000000</v>
+        <v>2959200</v>
       </c>
       <c r="G37" s="15">
-        <v>9050</v>
+        <v>8574.28</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0070766787066</v>
+        <v>0.0063254381296</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2762,25 +2825,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="F38" s="14">
-        <v>1887900</v>
+        <v>406000</v>
       </c>
       <c r="G38" s="15">
-        <v>7474.20</v>
+        <v>8190.64</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0058444764629</v>
+        <v>0.0060424183211</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2803,13 +2866,13 @@
         <v>96</v>
       </c>
       <c r="F39" s="14">
-        <v>493911</v>
+        <v>20000000</v>
       </c>
       <c r="G39" s="15">
-        <v>7315.56</v>
+        <v>7906</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0057204273678</v>
+        <v>0.0058324330268</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2829,16 +2892,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F40" s="14">
-        <v>406000</v>
+        <v>491492</v>
       </c>
       <c r="G40" s="15">
-        <v>7048.57</v>
+        <v>7811.28</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0055116536167</v>
+        <v>0.0057625559642</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2861,13 +2924,13 @@
         <v>101</v>
       </c>
       <c r="F41" s="14">
-        <v>2629550</v>
+        <v>1887900</v>
       </c>
       <c r="G41" s="15">
-        <v>6905.46</v>
+        <v>7500.63</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0053997482587</v>
+        <v>0.0055333825112</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2887,16 +2950,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F42" s="14">
-        <v>1524485</v>
+        <v>100000000</v>
       </c>
       <c r="G42" s="15">
-        <v>6822.07</v>
+        <v>6920</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0053345411607</v>
+        <v>0.0051050387737</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2919,13 +2982,13 @@
         <v>106</v>
       </c>
       <c r="F43" s="14">
-        <v>2468180</v>
+        <v>2610300</v>
       </c>
       <c r="G43" s="15">
-        <v>6581.40</v>
+        <v>6249.06</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0051463484243</v>
+        <v>0.0046100713294</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2945,16 +3008,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="F44" s="14">
-        <v>591782</v>
+        <v>598050</v>
       </c>
       <c r="G44" s="15">
-        <v>5865.74</v>
+        <v>5941.63</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0045867356195</v>
+        <v>0.0043832733424</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2974,16 +3037,16 @@
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="F45" s="14">
-        <v>598050</v>
+        <v>45650</v>
       </c>
       <c r="G45" s="15">
-        <v>5651.57</v>
+        <v>5623.62</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0044192646495</v>
+        <v>0.0041486702527</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -3003,16 +3066,16 @@
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="F46" s="14">
-        <v>106875</v>
+        <v>4414500</v>
       </c>
       <c r="G46" s="15">
-        <v>5482.31</v>
+        <v>5066.08</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0042869112088</v>
+        <v>0.0037373605247</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -3032,16 +3095,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F47" s="14">
-        <v>4414500</v>
+        <v>44150</v>
       </c>
       <c r="G47" s="15">
-        <v>4117.4</v>
+        <v>4949.22</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0032196151278</v>
+        <v>0.003651150289</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -3061,16 +3124,16 @@
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="F48" s="14">
-        <v>108325</v>
+        <v>86500</v>
       </c>
       <c r="G48" s="15">
-        <v>3780.81</v>
+        <v>4766.58</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0029564174166</v>
+        <v>0.003516412676</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -3081,25 +3144,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>119</v>
-      </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F49" s="14">
-        <v>2720250</v>
+        <v>1323000</v>
       </c>
       <c r="G49" s="15">
-        <v>3495.25</v>
+        <v>4212.43</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0027331227899</v>
+        <v>0.0031076038268</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -3110,25 +3173,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>121</v>
-      </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F50" s="14">
-        <v>1323000</v>
+        <v>2720250</v>
       </c>
       <c r="G50" s="15">
-        <v>3454.35</v>
+        <v>3861.94</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0027011408939</v>
+        <v>0.0028490395147</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -3139,25 +3202,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="D51" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>124</v>
-      </c>
       <c r="F51" s="14">
-        <v>1875300</v>
+        <v>108325</v>
       </c>
       <c r="G51" s="15">
-        <v>3321.53</v>
+        <v>3850.95</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0025972818369</v>
+        <v>0.0028409319459</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -3168,25 +3231,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="D52" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="F52" s="14">
-        <v>28100</v>
+        <v>1875300</v>
       </c>
       <c r="G52" s="15">
-        <v>3227.97</v>
+        <v>3559.32</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0025241222723</v>
+        <v>0.0026257899722</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -3206,16 +3269,16 @@
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="F53" s="14">
-        <v>1220067</v>
+        <v>867000</v>
       </c>
       <c r="G53" s="15">
-        <v>3211.22</v>
+        <v>3330.58</v>
       </c>
       <c r="H53" s="16">
-        <v>0.002511024552</v>
+        <v>0.0024570433582</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -3226,25 +3289,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="F54" s="14">
-        <v>867000</v>
+        <v>169125</v>
       </c>
       <c r="G54" s="15">
-        <v>3010.22</v>
+        <v>3064.88</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0023538519089</v>
+        <v>0.0022610305255</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -3255,25 +3318,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F55" s="14">
-        <v>49800</v>
+        <v>2880000</v>
       </c>
       <c r="G55" s="15">
-        <v>2945.25</v>
+        <v>3047.62</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0023030483934</v>
+        <v>0.0022482974375</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3284,25 +3347,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F56" s="14">
-        <v>2880000</v>
+        <v>150450</v>
       </c>
       <c r="G56" s="15">
-        <v>2914.56</v>
+        <v>2945.36</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0022790502421</v>
+        <v>0.0021728579483</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3313,25 +3376,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C57" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="F57" s="14">
-        <v>169125</v>
+        <v>281250</v>
       </c>
       <c r="G57" s="15">
-        <v>2509.14</v>
+        <v>2668.78</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0019620306751</v>
+        <v>0.0019688186963</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3342,25 +3405,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>139</v>
-      </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F58" s="14">
-        <v>281250</v>
+        <v>309282</v>
       </c>
       <c r="G58" s="15">
-        <v>2226.23</v>
+        <v>2526.68</v>
       </c>
       <c r="H58" s="16">
-        <v>0.001740808225</v>
+        <v>0.0018639883481</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3371,25 +3434,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="D59" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="F59" s="14">
         <v>288802</v>
       </c>
       <c r="G59" s="15">
-        <v>2156.34</v>
+        <v>1867.25</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0016861574986</v>
+        <v>0.0013775120881</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3400,25 +3463,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="D60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>32</v>
-      </c>
       <c r="F60" s="14">
-        <v>26250</v>
+        <v>475950</v>
       </c>
       <c r="G60" s="15">
-        <v>1363.50</v>
+        <v>1830.50</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0010661935266</v>
+        <v>0.0013504007912</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3438,16 +3501,16 @@
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="F61" s="14">
-        <v>45250</v>
+        <v>28800</v>
       </c>
       <c r="G61" s="15">
-        <v>1135.25</v>
+        <v>1432.54</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0008877126521</v>
+        <v>0.0010568167984</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3467,16 +3530,16 @@
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F62" s="14">
-        <v>42000</v>
+        <v>26250</v>
       </c>
       <c r="G62" s="15">
-        <v>780.57</v>
+        <v>1400.04</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0006103694031</v>
+        <v>0.0010328408215</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3496,16 +3559,16 @@
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F63" s="14">
-        <v>176850</v>
+        <v>45250</v>
       </c>
       <c r="G63" s="15">
-        <v>644.62</v>
+        <v>1151.97</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0005040628318</v>
+        <v>0.0008498340341</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3525,16 +3588,16 @@
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F64" s="14">
-        <v>8250</v>
+        <v>165200</v>
       </c>
       <c r="G64" s="15">
-        <v>561.87</v>
+        <v>1046.54</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0004393561839</v>
+        <v>0.000772055965</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3545,25 +3608,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="F65" s="14">
-        <v>312400</v>
+        <v>18150</v>
       </c>
       <c r="G65" s="15">
-        <v>441.30</v>
+        <v>920.01</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0003450760567</v>
+        <v>0.000678711954</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3583,16 +3646,16 @@
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>158</v>
+        <v>46</v>
       </c>
       <c r="F66" s="14">
-        <v>29400</v>
+        <v>42000</v>
       </c>
       <c r="G66" s="15">
-        <v>418.66</v>
+        <v>787.67</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0003273726306</v>
+        <v>0.0005810817761</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3603,25 +3666,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C67" s="13" t="s">
-        <v>160</v>
-      </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F67" s="14">
-        <v>105300</v>
+        <v>176850</v>
       </c>
       <c r="G67" s="15">
-        <v>224.70</v>
+        <v>694.67</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0001757049398</v>
+        <v>0.000512473596</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3632,25 +3695,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>162</v>
-      </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F68" s="14">
-        <v>3500</v>
+        <v>8250</v>
       </c>
       <c r="G68" s="15">
-        <v>86.03</v>
+        <v>567.64</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0000672714551</v>
+        <v>0.0004187607239</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3661,23 +3724,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="13"/>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="F69" s="14">
-        <v>-30000</v>
+        <v>312400</v>
       </c>
       <c r="G69" s="15">
-        <v>-24.65</v>
-      </c>
-      <c r="H69" s="17" t="s">
-        <v>164</v>
+        <v>478.35</v>
+      </c>
+      <c r="H69" s="16">
+        <v>0.0003528894938</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3690,21 +3755,23 @@
       <c r="B70" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C70" s="13"/>
+      <c r="C70" s="13" t="s">
+        <v>166</v>
+      </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c r="F70" s="14">
-        <v>-145000</v>
+        <v>29400</v>
       </c>
       <c r="G70" s="15">
-        <v>-36.83</v>
-      </c>
-      <c r="H70" s="17" t="s">
-        <v>164</v>
+        <v>446.91</v>
+      </c>
+      <c r="H70" s="16">
+        <v>0.0003296955026</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3715,23 +3782,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C71" s="13"/>
+        <v>168</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="F71" s="14">
-        <v>-210000</v>
+        <v>67000</v>
       </c>
       <c r="G71" s="15">
-        <v>-51.14</v>
-      </c>
-      <c r="H71" s="17" t="s">
-        <v>164</v>
+        <v>399.62</v>
+      </c>
+      <c r="H71" s="16">
+        <v>0.0002948086119</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3742,23 +3811,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C72" s="13"/>
+        <v>170</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>171</v>
+      </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F72" s="14">
-        <v>-432000</v>
+        <v>105300</v>
       </c>
       <c r="G72" s="15">
-        <v>-55.08</v>
-      </c>
-      <c r="H72" s="17" t="s">
-        <v>164</v>
+        <v>262.78</v>
+      </c>
+      <c r="H72" s="16">
+        <v>0.0001938586833</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3769,23 +3840,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C73" s="13"/>
+        <v>172</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F73" s="14">
-        <v>-140000</v>
+        <v>3500</v>
       </c>
       <c r="G73" s="15">
-        <v>-60.27</v>
-      </c>
-      <c r="H73" s="17" t="s">
-        <v>164</v>
+        <v>97.33</v>
+      </c>
+      <c r="H73" s="16">
+        <v>0.0000718025178</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3796,23 +3869,25 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C74" s="13"/>
+        <v>174</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>175</v>
+      </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="F74" s="14">
-        <v>-156750</v>
+        <v>31958</v>
       </c>
       <c r="G74" s="15">
-        <v>-63.25</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>164</v>
+        <v>87.88</v>
+      </c>
+      <c r="H74" s="16">
+        <v>0.0000648310415</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3823,23 +3898,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C75" s="13"/>
+        <v>177</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>178</v>
+      </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F75" s="14">
-        <v>-312500</v>
+        <v>3000</v>
       </c>
       <c r="G75" s="15">
-        <v>-68.59</v>
-      </c>
-      <c r="H75" s="16">
-        <v>-0.000053634187</v>
+        <v>23.53</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3850,23 +3927,23 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C76" s="13"/>
       <c r="D76" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F76" s="14">
-        <v>-262500</v>
+        <v>-36300</v>
       </c>
       <c r="G76" s="15">
-        <v>-72.45</v>
-      </c>
-      <c r="H76" s="16">
-        <v>-0.0000566525273</v>
+        <v>-8.77</v>
+      </c>
+      <c r="H76" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>13</v>
@@ -3877,23 +3954,23 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F77" s="14">
-        <v>-170000</v>
+        <v>-52000</v>
       </c>
       <c r="G77" s="15">
-        <v>-73.78</v>
-      </c>
-      <c r="H77" s="16">
-        <v>-0.0000576925254</v>
+        <v>-10.11</v>
+      </c>
+      <c r="H77" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>13</v>
@@ -3904,23 +3981,23 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C78" s="13"/>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F78" s="14">
-        <v>-550000</v>
+        <v>-100000</v>
       </c>
       <c r="G78" s="15">
-        <v>-83.60</v>
-      </c>
-      <c r="H78" s="16">
-        <v>-0.0000653713082</v>
+        <v>-27.10</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>13</v>
@@ -3931,23 +4008,23 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C79" s="13"/>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F79" s="14">
-        <v>-1275000</v>
+        <v>-12500</v>
       </c>
       <c r="G79" s="15">
-        <v>-84.79</v>
-      </c>
-      <c r="H79" s="16">
-        <v>-0.0000663018328</v>
+        <v>-27.36</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>13</v>
@@ -3958,23 +4035,23 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F80" s="14">
-        <v>-140000</v>
+        <v>-138125</v>
       </c>
       <c r="G80" s="15">
-        <v>-90.44</v>
-      </c>
-      <c r="H80" s="16">
-        <v>-0.0000707198698</v>
+        <v>-33.36</v>
+      </c>
+      <c r="H80" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>13</v>
@@ -3985,23 +4062,23 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C81" s="13"/>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F81" s="14">
-        <v>-618750</v>
+        <v>-79350</v>
       </c>
       <c r="G81" s="15">
-        <v>-92.81</v>
-      </c>
-      <c r="H81" s="16">
-        <v>-0.0000725730995</v>
+        <v>-47.29</v>
+      </c>
+      <c r="H81" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>13</v>
@@ -4012,23 +4089,23 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C82" s="13"/>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F82" s="14">
-        <v>-135000</v>
+        <v>-1125000</v>
       </c>
       <c r="G82" s="15">
-        <v>-100.04</v>
-      </c>
-      <c r="H82" s="16">
-        <v>-0.0000782266229</v>
+        <v>-51.19</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -4039,23 +4116,23 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C83" s="13"/>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F83" s="14">
-        <v>-382250</v>
+        <v>-199500</v>
       </c>
       <c r="G83" s="15">
-        <v>-100.15</v>
-      </c>
-      <c r="H83" s="16">
-        <v>-0.0000783126378</v>
+        <v>-54.36</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -4066,23 +4143,23 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C84" s="13"/>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F84" s="14">
-        <v>-500000</v>
+        <v>-960000</v>
       </c>
       <c r="G84" s="15">
-        <v>-121.25</v>
-      </c>
-      <c r="H84" s="16">
-        <v>-0.0000948118556</v>
+        <v>-60.96</v>
+      </c>
+      <c r="H84" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -4093,23 +4170,23 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C85" s="13"/>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F85" s="14">
-        <v>-270000</v>
+        <v>-343750</v>
       </c>
       <c r="G85" s="15">
-        <v>-128.25</v>
+        <v>-68.23</v>
       </c>
       <c r="H85" s="16">
-        <v>-0.0001002855297</v>
+        <v>-0.000050334797</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>13</v>
@@ -4120,23 +4197,23 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C86" s="13"/>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F86" s="14">
-        <v>-687500</v>
+        <v>-156100</v>
       </c>
       <c r="G86" s="15">
-        <v>-150.56</v>
+        <v>-68.37</v>
       </c>
       <c r="H86" s="16">
-        <v>-0.0001177309111</v>
+        <v>-0.0000504380781</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>13</v>
@@ -4147,23 +4224,23 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C87" s="13"/>
       <c r="D87" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F87" s="14">
-        <v>-400000</v>
+        <v>-206250</v>
       </c>
       <c r="G87" s="15">
-        <v>-163</v>
+        <v>-71.47</v>
       </c>
       <c r="H87" s="16">
-        <v>-0.000127458412</v>
+        <v>-0.0000527250175</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>13</v>
@@ -4174,23 +4251,23 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C88" s="13"/>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F88" s="14">
-        <v>-552500</v>
+        <v>-413700</v>
       </c>
       <c r="G88" s="15">
-        <v>-181.77</v>
+        <v>-74.67</v>
       </c>
       <c r="H88" s="16">
-        <v>-0.0001421356782</v>
+        <v>-0.000055085729</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>13</v>
@@ -4201,23 +4278,23 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C89" s="13"/>
       <c r="D89" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F89" s="14">
-        <v>-750000</v>
+        <v>-96250</v>
       </c>
       <c r="G89" s="15">
-        <v>-219.75</v>
+        <v>-84.80</v>
       </c>
       <c r="H89" s="16">
-        <v>-0.0001718342702</v>
+        <v>-0.0000625588566</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>13</v>
@@ -4228,6 +4305,25 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90" s="14">
+        <v>-2250000</v>
+      </c>
+      <c r="G90" s="15">
+        <v>-87.75</v>
+      </c>
+      <c r="H90" s="16">
+        <v>-0.0000647351376</v>
+      </c>
+      <c r="I90" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J90" s="11" t="s">
@@ -4235,28 +4331,26 @@
       </c>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I91" s="9" t="s">
+      <c r="B91" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" s="14">
+        <v>-500000</v>
+      </c>
+      <c r="G91" s="15">
+        <v>-107</v>
+      </c>
+      <c r="H91" s="16">
+        <v>-0.0000789362931</v>
+      </c>
+      <c r="I91" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J91" s="11" t="s">
@@ -4265,6 +4359,25 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="14">
+        <v>-581250</v>
+      </c>
+      <c r="G92" s="15">
+        <v>-108.40</v>
+      </c>
+      <c r="H92" s="16">
+        <v>-0.0000799691044</v>
+      </c>
+      <c r="I92" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J92" s="11" t="s">
@@ -4272,28 +4385,26 @@
       </c>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9">
-        <v>99019.74</v>
-      </c>
-      <c r="H93" s="10">
-        <v>0.07742882713720001</v>
-      </c>
-      <c r="I93" s="9" t="s">
+      <c r="B93" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C93" s="13"/>
+      <c r="D93" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="14">
+        <v>-500000</v>
+      </c>
+      <c r="G93" s="15">
+        <v>-119.50</v>
+      </c>
+      <c r="H93" s="16">
+        <v>-0.0000881578227</v>
+      </c>
+      <c r="I93" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J93" s="11" t="s">
@@ -4310,7 +4421,7 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="7" t="s">
-        <v>14</v>
+        <v>198</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>13</v>
@@ -4324,11 +4435,11 @@
       <c r="F95" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G95" s="9">
-        <v>79984.34</v>
-      </c>
-      <c r="H95" s="10">
-        <v>0.06254403046859999</v>
+      <c r="G95" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="I95" s="9" t="s">
         <v>13</v>
@@ -4347,7 +4458,7 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>13</v>
@@ -4362,10 +4473,10 @@
         <v>13</v>
       </c>
       <c r="G97" s="9">
-        <v>64806.96</v>
+        <v>120025.48999999996</v>
       </c>
       <c r="H97" s="10">
-        <v>0.050676025842399997</v>
+        <v>0.0885454884807</v>
       </c>
       <c r="I97" s="9" t="s">
         <v>13</v>
@@ -4376,57 +4487,36 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D98" s="18">
-        <v>7.18</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F98" s="14">
-        <v>19256950</v>
-      </c>
-      <c r="G98" s="15">
-        <v>19783.53</v>
-      </c>
-      <c r="H98" s="16">
-        <v>0.015469799502</v>
-      </c>
-      <c r="I98" s="15">
-        <v>6.87</v>
+        <v>13</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="D99" s="18">
-        <v>7.10</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F99" s="14">
-        <v>14648000</v>
-      </c>
-      <c r="G99" s="15">
-        <v>15000.49</v>
-      </c>
-      <c r="H99" s="16">
-        <v>0.0117296848809</v>
-      </c>
-      <c r="I99" s="15">
-        <v>6.86</v>
+      <c r="B99" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="9">
+        <v>102875.68999999997</v>
+      </c>
+      <c r="H99" s="10">
+        <v>0.0758936974458</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
@@ -4434,57 +4524,36 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D100" s="18">
-        <v>7.06</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F100" s="14">
-        <v>13000000</v>
-      </c>
-      <c r="G100" s="15">
-        <v>13161.45</v>
-      </c>
-      <c r="H100" s="16">
-        <v>0.0102916412114</v>
-      </c>
-      <c r="I100" s="15">
-        <v>6.73</v>
+        <v>13</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C101" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="D101" s="18">
-        <v>7.53</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F101" s="14">
-        <v>12641120</v>
-      </c>
-      <c r="G101" s="15">
-        <v>12733.24</v>
-      </c>
-      <c r="H101" s="16">
-        <v>0.0099568009254</v>
-      </c>
-      <c r="I101" s="15">
-        <v>7.47</v>
+      <c r="B101" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="9">
+        <v>82387.10999999999</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0.060778813729299996</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4492,28 +4561,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D102" s="18">
-        <v>7.26</v>
+        <v>6.79</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="F102" s="14">
-        <v>4003300</v>
+        <v>36224650</v>
       </c>
       <c r="G102" s="15">
-        <v>4128.25</v>
+        <v>37526.17</v>
       </c>
       <c r="H102" s="16">
-        <v>0.0032280993227</v>
+        <v>0.027683894925</v>
       </c>
       <c r="I102" s="15">
-        <v>6.86</v>
+        <v>6.37</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4521,36 +4590,57 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>13</v>
+        <v>201</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D103" s="18">
+        <v>7.10</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F103" s="14">
+        <v>14648000</v>
+      </c>
+      <c r="G103" s="15">
+        <v>15441.63</v>
+      </c>
+      <c r="H103" s="16">
+        <v>0.0113916358208</v>
+      </c>
+      <c r="I103" s="15">
+        <v>6.39</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="9">
-        <v>15177.38</v>
-      </c>
-      <c r="H104" s="10">
-        <v>0.011868004626200001</v>
-      </c>
-      <c r="I104" s="9" t="s">
-        <v>13</v>
+      <c r="B104" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D104" s="18">
+        <v>6.99</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F104" s="14">
+        <v>12641120</v>
+      </c>
+      <c r="G104" s="15">
+        <v>12903.60</v>
+      </c>
+      <c r="H104" s="16">
+        <v>0.0095192743238</v>
+      </c>
+      <c r="I104" s="15">
+        <v>6.80</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4558,28 +4648,28 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D105" s="18">
-        <v>9.09</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F105" s="14">
-        <v>7500</v>
+        <v>7000000</v>
       </c>
       <c r="G105" s="15">
-        <v>7623.50</v>
+        <v>7264.29</v>
       </c>
       <c r="H105" s="16">
-        <v>0.0059612221127</v>
+        <v>0.0053590292072</v>
       </c>
       <c r="I105" s="15">
-        <v>8.60</v>
+        <v>6.82</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
@@ -4587,28 +4677,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D106" s="18">
-        <v>8.40</v>
+        <v>7.12</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F106" s="14">
-        <v>5000</v>
+        <v>7000000</v>
       </c>
       <c r="G106" s="15">
-        <v>5018.94</v>
+        <v>7235.47</v>
       </c>
       <c r="H106" s="16">
-        <v>0.0039245774395</v>
+        <v>0.0053377680486</v>
       </c>
       <c r="I106" s="15">
-        <v>8.2</v>
+        <v>6.83</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4616,28 +4706,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D107" s="18">
-        <v>8.75</v>
+        <v>7.13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F107" s="14">
-        <v>2500</v>
+        <v>1331200</v>
       </c>
       <c r="G107" s="15">
-        <v>2497.41</v>
+        <v>1375.06</v>
       </c>
       <c r="H107" s="16">
-        <v>0.0019528583611</v>
+        <v>0.0010144125168</v>
       </c>
       <c r="I107" s="15">
-        <v>8.67</v>
+        <v>6.75</v>
       </c>
       <c r="J107" s="11" t="s">
         <v>13</v>
@@ -4645,28 +4735,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="12" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C108" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D108" s="18">
+        <v>7.29</v>
+      </c>
+      <c r="E108" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D108" s="18">
-        <v>8.49</v>
-      </c>
-      <c r="E108" s="13" t="s">
-        <v>204</v>
-      </c>
       <c r="F108" s="14">
-        <v>750000</v>
+        <v>577700</v>
       </c>
       <c r="G108" s="15">
-        <v>37.53</v>
-      </c>
-      <c r="H108" s="17" t="s">
-        <v>164</v>
+        <v>603.04</v>
+      </c>
+      <c r="H108" s="16">
+        <v>0.0004448760956</v>
       </c>
       <c r="I108" s="15">
-        <v>7.32</v>
+        <v>6.88</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4674,35 +4764,35 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
-        <v>13</v>
+        <v>201</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D109" s="18">
+        <v>7.26</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F109" s="14">
+        <v>35600</v>
+      </c>
+      <c r="G109" s="15">
+        <v>37.85</v>
+      </c>
+      <c r="H109" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="I109" s="15">
+        <v>6.31</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
-      <c r="B110" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H110" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I110" s="9" t="s">
+      <c r="B110" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J110" s="11" t="s">
@@ -4710,7 +4800,28 @@
       </c>
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="9">
+        <v>20488.58</v>
+      </c>
+      <c r="H111" s="10">
+        <v>0.015114883716499999</v>
+      </c>
+      <c r="I111" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="11" t="s">
@@ -4718,29 +4829,29 @@
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H112" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I112" s="9" t="s">
-        <v>13</v>
+      <c r="B112" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D112" s="18">
+        <v>9.09</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F112" s="14">
+        <v>7500</v>
+      </c>
+      <c r="G112" s="15">
+        <v>7731.77</v>
+      </c>
+      <c r="H112" s="16">
+        <v>0.0057038996589</v>
+      </c>
+      <c r="I112" s="15">
+        <v>8.15</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>13</v>
@@ -4748,36 +4859,57 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
-        <v>13</v>
+        <v>218</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D113" s="18">
+        <v>7.58</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="F113" s="14">
+        <v>5000</v>
+      </c>
+      <c r="G113" s="15">
+        <v>5125.01</v>
+      </c>
+      <c r="H113" s="16">
+        <v>0.0037808345037</v>
+      </c>
+      <c r="I113" s="15">
+        <v>7.21</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="9">
-        <v>19035.40</v>
-      </c>
-      <c r="H114" s="10">
-        <v>0.0148847966686</v>
-      </c>
-      <c r="I114" s="9" t="s">
-        <v>13</v>
+      <c r="B114" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D114" s="18">
+        <v>8.40</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F114" s="14">
+        <v>5000</v>
+      </c>
+      <c r="G114" s="15">
+        <v>5109.29</v>
+      </c>
+      <c r="H114" s="16">
+        <v>0.0037692375081</v>
+      </c>
+      <c r="I114" s="15">
+        <v>7.28</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>13</v>
@@ -4785,28 +4917,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>13</v>
+        <v>224</v>
+      </c>
+      <c r="D115" s="18">
+        <v>8.75</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F115" s="14">
-        <v>73</v>
+        <v>2500</v>
       </c>
       <c r="G115" s="15">
-        <v>6597.17</v>
+        <v>2522.51</v>
       </c>
       <c r="H115" s="16">
-        <v>0.0051586798301</v>
+        <v>0.0018609120458</v>
       </c>
       <c r="I115" s="15">
-        <v>8.35</v>
+        <v>7.96</v>
       </c>
       <c r="J115" s="11" t="s">
         <v>13</v>
@@ -4814,57 +4946,36 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
       <c r="B116" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C116" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="F116" s="14">
-        <v>65</v>
-      </c>
-      <c r="G116" s="15">
-        <v>6256.93</v>
-      </c>
-      <c r="H116" s="16">
-        <v>0.0048926279889</v>
-      </c>
-      <c r="I116" s="15">
-        <v>8.41</v>
+        <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C117" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="F117" s="14">
-        <v>62</v>
-      </c>
-      <c r="G117" s="15">
-        <v>6181.30</v>
-      </c>
-      <c r="H117" s="16">
-        <v>0.0048334888496</v>
-      </c>
-      <c r="I117" s="15">
-        <v>8.41</v>
+      <c r="B117" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
@@ -4880,7 +4991,7 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>13</v>
@@ -4895,10 +5006,10 @@
         <v>13</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="I119" s="9" t="s">
         <v>13</v>
@@ -4917,7 +5028,7 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="7" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>13</v>
@@ -4931,11 +5042,11 @@
       <c r="F121" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G121" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>185</v>
+      <c r="G121" s="9">
+        <v>17149.80</v>
+      </c>
+      <c r="H121" s="10">
+        <v>0.012651791034899999</v>
       </c>
       <c r="I121" s="9" t="s">
         <v>13</v>
@@ -4946,36 +5057,57 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
-        <v>13</v>
+        <v>228</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F122" s="14">
+        <v>62</v>
+      </c>
+      <c r="G122" s="15">
+        <v>6177.68</v>
+      </c>
+      <c r="H122" s="16">
+        <v>0.0045574127069</v>
+      </c>
+      <c r="I122" s="15">
+        <v>7.76</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I123" s="9" t="s">
-        <v>13</v>
+      <c r="B123" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F123" s="14">
+        <v>65</v>
+      </c>
+      <c r="G123" s="15">
+        <v>5799.40</v>
+      </c>
+      <c r="H123" s="16">
+        <v>0.0042783470902</v>
+      </c>
+      <c r="I123" s="15">
+        <v>7.58</v>
       </c>
       <c r="J123" s="11" t="s">
         <v>13</v>
@@ -4983,35 +5115,35 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
       <c r="B124" s="12" t="s">
-        <v>13</v>
+        <v>228</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F124" s="14">
+        <v>73</v>
+      </c>
+      <c r="G124" s="15">
+        <v>5172.72</v>
+      </c>
+      <c r="H124" s="16">
+        <v>0.0038160312378</v>
+      </c>
+      <c r="I124" s="15">
+        <v>7.39</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
-      <c r="B125" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G125" s="9">
-        <v>67007.01000000001</v>
-      </c>
-      <c r="H125" s="10">
-        <v>0.0523963625263</v>
-      </c>
-      <c r="I125" s="9" t="s">
+      <c r="B125" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J125" s="11" t="s">
@@ -5019,7 +5151,28 @@
       </c>
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
-      <c r="B126" s="12" t="s">
+      <c r="B126" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H126" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I126" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J126" s="11" t="s">
@@ -5027,28 +5180,7 @@
       </c>
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
-      <c r="B127" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="9">
-        <v>67007.01000000001</v>
-      </c>
-      <c r="H127" s="10">
-        <v>0.0523963625263</v>
-      </c>
-      <c r="I127" s="9" t="s">
+      <c r="B127" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J127" s="11" t="s">
@@ -5056,29 +5188,29 @@
       </c>
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
-      <c r="B128" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C128" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F128" s="14">
-        <v>5000</v>
-      </c>
-      <c r="G128" s="15">
-        <v>23621.03</v>
-      </c>
-      <c r="H128" s="16">
-        <v>0.0184705458597</v>
-      </c>
-      <c r="I128" s="15">
-        <v>7.64</v>
+      <c r="B128" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>13</v>
@@ -5086,57 +5218,36 @@
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
       <c r="B129" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C129" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F129" s="14">
-        <v>4000</v>
-      </c>
-      <c r="G129" s="15">
-        <v>18668.38</v>
-      </c>
-      <c r="H129" s="16">
-        <v>0.0145978041142</v>
-      </c>
-      <c r="I129" s="15">
-        <v>7.64</v>
+        <v>13</v>
       </c>
       <c r="J129" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1">
-      <c r="B130" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C130" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E130" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F130" s="14">
-        <v>3000</v>
-      </c>
-      <c r="G130" s="15">
-        <v>14943.21</v>
-      </c>
-      <c r="H130" s="16">
-        <v>0.0116848945874</v>
-      </c>
-      <c r="I130" s="15">
-        <v>7.30</v>
+      <c r="B130" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I130" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>13</v>
@@ -5144,35 +5255,35 @@
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1">
       <c r="B131" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="C131" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F131" s="14">
-        <v>2000</v>
-      </c>
-      <c r="G131" s="15">
-        <v>9774.39</v>
-      </c>
-      <c r="H131" s="16">
-        <v>0.007643117965</v>
-      </c>
-      <c r="I131" s="15">
-        <v>7.59</v>
+        <v>13</v>
       </c>
       <c r="J131" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1">
-      <c r="B132" s="12" t="s">
+      <c r="B132" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="9">
+        <v>69761.73</v>
+      </c>
+      <c r="H132" s="10">
+        <v>0.051464788522399996</v>
+      </c>
+      <c r="I132" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J132" s="11" t="s">
@@ -5180,28 +5291,7 @@
       </c>
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1">
-      <c r="B133" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I133" s="9" t="s">
+      <c r="B133" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J133" s="11" t="s">
@@ -5209,7 +5299,28 @@
       </c>
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="9">
+        <v>69761.73</v>
+      </c>
+      <c r="H134" s="10">
+        <v>0.051464788522399996</v>
+      </c>
+      <c r="I134" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J134" s="11" t="s">
@@ -5217,29 +5328,29 @@
       </c>
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1">
-      <c r="B135" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G135" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I135" s="9" t="s">
-        <v>13</v>
+      <c r="B135" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C135" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F135" s="14">
+        <v>5000</v>
+      </c>
+      <c r="G135" s="15">
+        <v>24313.43</v>
+      </c>
+      <c r="H135" s="16">
+        <v>0.0179365611089</v>
+      </c>
+      <c r="I135" s="15">
+        <v>6.48</v>
       </c>
       <c r="J135" s="11" t="s">
         <v>13</v>
@@ -5247,36 +5358,57 @@
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1">
       <c r="B136" s="12" t="s">
-        <v>13</v>
+        <v>241</v>
+      </c>
+      <c r="C136" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F136" s="14">
+        <v>4000</v>
+      </c>
+      <c r="G136" s="15">
+        <v>19248.30</v>
+      </c>
+      <c r="H136" s="16">
+        <v>0.0141999014204</v>
+      </c>
+      <c r="I136" s="15">
+        <v>6.45</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1">
-      <c r="B137" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G137" s="9">
-        <v>106836.43</v>
-      </c>
-      <c r="H137" s="10">
-        <v>0.0835411148373</v>
-      </c>
-      <c r="I137" s="9" t="s">
-        <v>13</v>
+      <c r="B137" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F137" s="14">
+        <v>4000</v>
+      </c>
+      <c r="G137" s="15">
+        <v>19056.28</v>
+      </c>
+      <c r="H137" s="16">
+        <v>0.0140582439716</v>
+      </c>
+      <c r="I137" s="15">
+        <v>6.41</v>
       </c>
       <c r="J137" s="11" t="s">
         <v>13</v>
@@ -5284,28 +5416,28 @@
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1">
       <c r="B138" s="12" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="F138" s="14">
-        <v>28776141.243</v>
+        <v>1500</v>
       </c>
       <c r="G138" s="15">
-        <v>106836.43</v>
+        <v>7143.72</v>
       </c>
       <c r="H138" s="16">
-        <v>0.0835411148373</v>
-      </c>
-      <c r="I138" s="15" t="s">
-        <v>13</v>
+        <v>0.0052700820215</v>
+      </c>
+      <c r="I138" s="15">
+        <v>6.43</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>13</v>
@@ -5321,7 +5453,7 @@
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
       <c r="B140" s="7" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>13</v>
@@ -5335,11 +5467,11 @@
       <c r="F140" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G140" s="9">
-        <v>49459.95</v>
-      </c>
-      <c r="H140" s="10">
-        <v>0.0386753784528</v>
+      <c r="G140" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="I140" s="9" t="s">
         <v>13</v>
@@ -5358,7 +5490,7 @@
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1">
       <c r="B142" s="7" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>13</v>
@@ -5372,11 +5504,11 @@
       <c r="F142" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G142" s="9">
-        <v>22974.03</v>
-      </c>
-      <c r="H142" s="10">
-        <v>0.0179646219786</v>
+      <c r="G142" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="I142" s="9" t="s">
         <v>13</v>
@@ -5387,27 +5519,6 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1">
       <c r="B143" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C143" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E143" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F143" s="14">
-        <v>4452835</v>
-      </c>
-      <c r="G143" s="15">
-        <v>13275.24</v>
-      </c>
-      <c r="H143" s="16">
-        <v>0.0103806196943</v>
-      </c>
-      <c r="I143" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J143" s="11" t="s">
@@ -5415,28 +5526,28 @@
       </c>
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1">
-      <c r="B144" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C144" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F144" s="14">
-        <v>1523199</v>
-      </c>
-      <c r="G144" s="15">
-        <v>5696.76</v>
-      </c>
-      <c r="H144" s="16">
-        <v>0.0044546011258</v>
-      </c>
-      <c r="I144" s="15" t="s">
+      <c r="B144" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144" s="9">
+        <v>160905.38</v>
+      </c>
+      <c r="H144" s="10">
+        <v>0.1187034976604</v>
+      </c>
+      <c r="I144" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J144" s="11" t="s">
@@ -5445,25 +5556,25 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1">
       <c r="B145" s="12" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="D145" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="F145" s="14">
-        <v>2886635</v>
+        <v>42056882.017</v>
       </c>
       <c r="G145" s="15">
-        <v>4002.03</v>
+        <v>160905.38</v>
       </c>
       <c r="H145" s="16">
-        <v>0.0031294011585</v>
+        <v>0.1187034976604</v>
       </c>
       <c r="I145" s="15" t="s">
         <v>13</v>
@@ -5482,7 +5593,7 @@
     </row>
     <row r="147" spans="2:10" ht="15" customHeight="1">
       <c r="B147" s="7" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>13</v>
@@ -5496,11 +5607,11 @@
       <c r="F147" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G147" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>185</v>
+      <c r="G147" s="9">
+        <v>18741.69</v>
+      </c>
+      <c r="H147" s="10">
+        <v>0.0138261638924</v>
       </c>
       <c r="I147" s="9" t="s">
         <v>13</v>
@@ -5511,6 +5622,27 @@
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1">
       <c r="B148" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F148" s="14">
+        <v>2820667</v>
+      </c>
+      <c r="G148" s="15">
+        <v>8629.55</v>
+      </c>
+      <c r="H148" s="16">
+        <v>0.0063662120448</v>
+      </c>
+      <c r="I148" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J148" s="11" t="s">
@@ -5518,28 +5650,28 @@
       </c>
     </row>
     <row r="149" spans="2:10" ht="15" customHeight="1">
-      <c r="B149" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D149" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F149" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G149" s="9">
-        <v>63933.62</v>
-      </c>
-      <c r="H149" s="10">
-        <v>0.049993114618000004</v>
-      </c>
-      <c r="I149" s="9" t="s">
+      <c r="B149" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F149" s="14">
+        <v>1442853</v>
+      </c>
+      <c r="G149" s="15">
+        <v>5698.98</v>
+      </c>
+      <c r="H149" s="16">
+        <v>0.0042042650102</v>
+      </c>
+      <c r="I149" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J149" s="11" t="s">
@@ -5548,6 +5680,27 @@
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1">
       <c r="B150" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C150" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F150" s="14">
+        <v>3271432</v>
+      </c>
+      <c r="G150" s="15">
+        <v>4413.16</v>
+      </c>
+      <c r="H150" s="16">
+        <v>0.0032556868374</v>
+      </c>
+      <c r="I150" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J150" s="11" t="s">
@@ -5555,286 +5708,233 @@
       </c>
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1">
-      <c r="B151" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C151" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D151" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G151" s="20">
-        <v>-4422.992794079939</v>
-      </c>
-      <c r="H151" s="21">
-        <v>-0.003458574466919051</v>
-      </c>
-      <c r="I151" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J151" s="22" t="s">
+      <c r="B151" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J151" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1">
-      <c r="B152" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="C152" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D152" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E152" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F152" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G152" s="20">
-        <v>1278848.50720592</v>
-      </c>
-      <c r="H152" s="21">
-        <v>0.9999999999967808</v>
-      </c>
-      <c r="I152" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J152" s="22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="154" spans="2:8" ht="15" customHeight="1">
-      <c r="B154" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="C154" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D154" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E154" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F154" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G154" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="H154" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="155" spans="2:8" ht="15" customHeight="1">
-      <c r="B155" s="20" t="s">
+      <c r="B152" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J152" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" ht="15" customHeight="1">
+      <c r="B153" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J153" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" ht="15" customHeight="1">
+      <c r="B154" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154" s="9">
+        <v>70192.36</v>
+      </c>
+      <c r="H154" s="10">
+        <v>0.051782473905</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J154" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" ht="15" customHeight="1">
+      <c r="B155" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J155" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" ht="15" customHeight="1">
+      <c r="B156" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="C156" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D156" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="20">
+        <v>-28780.05514621036</v>
+      </c>
+      <c r="H156" s="21">
+        <v>-0.021231690380486286</v>
+      </c>
+      <c r="I156" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J156" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="2:10" ht="15" customHeight="1">
+      <c r="B157" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C157" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="20">
+        <v>1355523.49485379</v>
+      </c>
+      <c r="H157" s="21">
+        <v>0.9999999999958133</v>
+      </c>
+      <c r="I157" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J157" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" spans="2:8" ht="15" customHeight="1">
+      <c r="B159" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C159" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H159" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="2:8" ht="15" customHeight="1">
+      <c r="B160" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C155" s="20" t="s">
+      <c r="C160" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="20" t="s">
+      <c r="D160" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E155" s="20" t="s">
+      <c r="E160" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F155" s="20" t="s">
+      <c r="F160" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G155" s="20" t="s">
+      <c r="G160" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H155" s="20" t="s">
+      <c r="H160" s="20" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="2:8" ht="15" customHeight="1">
-      <c r="B156" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H156" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="157" spans="2:10" ht="15" customHeight="1">
-      <c r="B157" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="C157" s="13"/>
-      <c r="D157" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E157" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F157" s="14">
-        <v>-3500</v>
-      </c>
-      <c r="G157" s="15">
-        <v>-86.29</v>
-      </c>
-      <c r="H157" s="16">
-        <v>-0.000067474763</v>
-      </c>
-      <c r="I157" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J157" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="158" spans="2:10" ht="15" customHeight="1">
-      <c r="B158" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="C158" s="13"/>
-      <c r="D158" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E158" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F158" s="14">
-        <v>-105300</v>
-      </c>
-      <c r="G158" s="15">
-        <v>-225.42</v>
-      </c>
-      <c r="H158" s="16">
-        <v>-0.0001762679463</v>
-      </c>
-      <c r="I158" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J158" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="159" spans="2:10" ht="15" customHeight="1">
-      <c r="B159" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="C159" s="13"/>
-      <c r="D159" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F159" s="14">
-        <v>-29400</v>
-      </c>
-      <c r="G159" s="15">
-        <v>-420.85</v>
-      </c>
-      <c r="H159" s="16">
-        <v>-0.0003290851086</v>
-      </c>
-      <c r="I159" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J159" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="160" spans="2:10" ht="15" customHeight="1">
-      <c r="B160" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C160" s="13"/>
-      <c r="D160" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E160" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F160" s="14">
-        <v>-312400</v>
-      </c>
-      <c r="G160" s="15">
-        <v>-443.92</v>
-      </c>
-      <c r="H160" s="16">
-        <v>-0.0003471247747</v>
-      </c>
-      <c r="I160" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J160" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="161" spans="2:10" ht="15" customHeight="1">
-      <c r="B161" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C161" s="13"/>
-      <c r="D161" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E161" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="F161" s="14">
-        <v>-8250</v>
-      </c>
-      <c r="G161" s="15">
-        <v>-565.23</v>
-      </c>
-      <c r="H161" s="16">
-        <v>-0.0004419835475</v>
-      </c>
-      <c r="I161" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J161" s="11" t="s">
+    <row r="161" spans="2:8" ht="15" customHeight="1">
+      <c r="B161" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H161" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1">
       <c r="B162" s="12" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C162" s="13"/>
       <c r="D162" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F162" s="14">
-        <v>-176850</v>
+        <v>-3000</v>
       </c>
       <c r="G162" s="15">
-        <v>-647.89</v>
-      </c>
-      <c r="H162" s="16">
-        <v>-0.0005066198195</v>
+        <v>-23.54</v>
+      </c>
+      <c r="H162" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="I162" s="15" t="s">
         <v>13</v>
@@ -5845,23 +5945,23 @@
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1">
       <c r="B163" s="12" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C163" s="13"/>
       <c r="D163" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F163" s="14">
-        <v>-42000</v>
+        <v>-3500</v>
       </c>
       <c r="G163" s="15">
-        <v>-785.06</v>
+        <v>-97.87</v>
       </c>
       <c r="H163" s="16">
-        <v>-0.000613880374</v>
+        <v>-0.0000722008879</v>
       </c>
       <c r="I163" s="15" t="s">
         <v>13</v>
@@ -5872,23 +5972,23 @@
     </row>
     <row r="164" spans="2:10" ht="15" customHeight="1">
       <c r="B164" s="12" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C164" s="13"/>
       <c r="D164" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F164" s="14">
-        <v>-45250</v>
+        <v>-105300</v>
       </c>
       <c r="G164" s="15">
-        <v>-1139.67</v>
+        <v>-264.73</v>
       </c>
       <c r="H164" s="16">
-        <v>-0.0008911688863</v>
+        <v>-0.0001952972419</v>
       </c>
       <c r="I164" s="15" t="s">
         <v>13</v>
@@ -5899,23 +5999,23 @@
     </row>
     <row r="165" spans="2:10" ht="15" customHeight="1">
       <c r="B165" s="12" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C165" s="13"/>
       <c r="D165" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F165" s="14">
-        <v>-26250</v>
+        <v>-67000</v>
       </c>
       <c r="G165" s="15">
-        <v>-1369.99</v>
+        <v>-402.10</v>
       </c>
       <c r="H165" s="16">
-        <v>-0.0010712684045</v>
+        <v>-0.0002966381634</v>
       </c>
       <c r="I165" s="15" t="s">
         <v>13</v>
@@ -5926,23 +6026,23 @@
     </row>
     <row r="166" spans="2:10" ht="15" customHeight="1">
       <c r="B166" s="12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C166" s="13"/>
       <c r="D166" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="F166" s="14">
-        <v>-150000</v>
+        <v>-29400</v>
       </c>
       <c r="G166" s="15">
-        <v>-1497</v>
+        <v>-449</v>
       </c>
       <c r="H166" s="16">
-        <v>-0.001170584312</v>
+        <v>-0.0003312373424</v>
       </c>
       <c r="I166" s="15" t="s">
         <v>13</v>
@@ -5953,23 +6053,23 @@
     </row>
     <row r="167" spans="2:10" ht="15" customHeight="1">
       <c r="B167" s="12" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C167" s="13"/>
       <c r="D167" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E167" s="13" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="F167" s="14">
-        <v>-36900</v>
+        <v>-312400</v>
       </c>
       <c r="G167" s="15">
-        <v>-1887.27</v>
+        <v>-478.82</v>
       </c>
       <c r="H167" s="16">
-        <v>-0.0014757572842</v>
+        <v>-0.0003532362233</v>
       </c>
       <c r="I167" s="15" t="s">
         <v>13</v>
@@ -5980,23 +6080,23 @@
     </row>
     <row r="168" spans="2:10" ht="15" customHeight="1">
       <c r="B168" s="12" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C168" s="13"/>
       <c r="D168" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E168" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F168" s="14">
-        <v>-288000</v>
+        <v>-8250</v>
       </c>
       <c r="G168" s="15">
-        <v>-2160</v>
+        <v>-571.44</v>
       </c>
       <c r="H168" s="16">
-        <v>-0.0016890194482</v>
+        <v>-0.0004215640689</v>
       </c>
       <c r="I168" s="15" t="s">
         <v>13</v>
@@ -6007,23 +6107,23 @@
     </row>
     <row r="169" spans="2:10" ht="15" customHeight="1">
       <c r="B169" s="12" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C169" s="13"/>
       <c r="D169" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E169" s="13" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="F169" s="14">
-        <v>-281250</v>
+        <v>-176850</v>
       </c>
       <c r="G169" s="15">
-        <v>-2232.14</v>
+        <v>-693.34</v>
       </c>
       <c r="H169" s="16">
-        <v>-0.0017454295699</v>
+        <v>-0.0005114924253</v>
       </c>
       <c r="I169" s="15" t="s">
         <v>13</v>
@@ -6034,23 +6134,23 @@
     </row>
     <row r="170" spans="2:10" ht="15" customHeight="1">
       <c r="B170" s="12" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C170" s="13"/>
       <c r="D170" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E170" s="13" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F170" s="14">
-        <v>-169125</v>
+        <v>-42000</v>
       </c>
       <c r="G170" s="15">
-        <v>-2517.43</v>
+        <v>-788.76</v>
       </c>
       <c r="H170" s="16">
-        <v>-0.0019685130692</v>
+        <v>-0.0005818858935</v>
       </c>
       <c r="I170" s="15" t="s">
         <v>13</v>
@@ -6061,23 +6161,23 @@
     </row>
     <row r="171" spans="2:10" ht="15" customHeight="1">
       <c r="B171" s="12" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C171" s="13"/>
       <c r="D171" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E171" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F171" s="14">
-        <v>-2880000</v>
+        <v>-18150</v>
       </c>
       <c r="G171" s="15">
-        <v>-2932.7000000000003</v>
+        <v>-924.96</v>
       </c>
       <c r="H171" s="16">
-        <v>-0.0022932348776</v>
+        <v>-0.0006823636797</v>
       </c>
       <c r="I171" s="15" t="s">
         <v>13</v>
@@ -6088,23 +6188,23 @@
     </row>
     <row r="172" spans="2:10" ht="15" customHeight="1">
       <c r="B172" s="12" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C172" s="13"/>
       <c r="D172" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E172" s="13" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="F172" s="14">
-        <v>-49800</v>
+        <v>-165200</v>
       </c>
       <c r="G172" s="15">
-        <v>-2944</v>
+        <v>-1053.15</v>
       </c>
       <c r="H172" s="16">
-        <v>-0.0023020709516</v>
+        <v>-0.0007769323099</v>
       </c>
       <c r="I172" s="15" t="s">
         <v>13</v>
@@ -6115,23 +6215,23 @@
     </row>
     <row r="173" spans="2:10" ht="15" customHeight="1">
       <c r="B173" s="12" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C173" s="13"/>
       <c r="D173" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E173" s="13" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="F173" s="14">
-        <v>-127800</v>
+        <v>-45250</v>
       </c>
       <c r="G173" s="15">
-        <v>-2955.76</v>
+        <v>-1158.49</v>
       </c>
       <c r="H173" s="16">
-        <v>-0.0023112667242</v>
+        <v>-0.0008546439839</v>
       </c>
       <c r="I173" s="15" t="s">
         <v>13</v>
@@ -6142,23 +6242,23 @@
     </row>
     <row r="174" spans="2:10" ht="15" customHeight="1">
       <c r="B174" s="12" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C174" s="13"/>
       <c r="D174" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E174" s="13" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="F174" s="14">
-        <v>-867000</v>
+        <v>-26250</v>
       </c>
       <c r="G174" s="15">
-        <v>-3023.23</v>
+        <v>-1409.36</v>
       </c>
       <c r="H174" s="16">
-        <v>-0.0023640251233</v>
+        <v>-0.0010397163939</v>
       </c>
       <c r="I174" s="15" t="s">
         <v>13</v>
@@ -6169,23 +6269,23 @@
     </row>
     <row r="175" spans="2:10" ht="15" customHeight="1">
       <c r="B175" s="12" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C175" s="13"/>
       <c r="D175" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E175" s="13" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="F175" s="14">
-        <v>-28100</v>
+        <v>-28800</v>
       </c>
       <c r="G175" s="15">
-        <v>-3253.36</v>
+        <v>-1441.93</v>
       </c>
       <c r="H175" s="16">
-        <v>-0.0025439760704</v>
+        <v>-0.0010637440114</v>
       </c>
       <c r="I175" s="15" t="s">
         <v>13</v>
@@ -6196,23 +6296,23 @@
     </row>
     <row r="176" spans="2:10" ht="15" customHeight="1">
       <c r="B176" s="12" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C176" s="13"/>
       <c r="D176" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E176" s="13" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="F176" s="14">
-        <v>-1875300</v>
+        <v>-475950</v>
       </c>
       <c r="G176" s="15">
-        <v>-3337.66</v>
+        <v>-1842.16</v>
       </c>
       <c r="H176" s="16">
-        <v>-0.002609894746</v>
+        <v>-0.001359002634</v>
       </c>
       <c r="I176" s="15" t="s">
         <v>13</v>
@@ -6223,23 +6323,23 @@
     </row>
     <row r="177" spans="2:10" ht="15" customHeight="1">
       <c r="B177" s="12" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C177" s="13"/>
       <c r="D177" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E177" s="13" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="F177" s="14">
-        <v>-1323000</v>
+        <v>-288000</v>
       </c>
       <c r="G177" s="15">
-        <v>-3471.55</v>
+        <v>-1871.14</v>
       </c>
       <c r="H177" s="16">
-        <v>-0.0027145904932</v>
+        <v>-0.0013803818282</v>
       </c>
       <c r="I177" s="15" t="s">
         <v>13</v>
@@ -6250,7 +6350,7 @@
     </row>
     <row r="178" spans="2:10" ht="15" customHeight="1">
       <c r="B178" s="12" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C178" s="13"/>
       <c r="D178" s="13" t="s">
@@ -6260,13 +6360,13 @@
         <v>17</v>
       </c>
       <c r="F178" s="14">
-        <v>-2720250</v>
+        <v>-300000</v>
       </c>
       <c r="G178" s="15">
-        <v>-3515.92</v>
+        <v>-2460</v>
       </c>
       <c r="H178" s="16">
-        <v>-0.0027492857677</v>
+        <v>-0.0018147970207</v>
       </c>
       <c r="I178" s="15" t="s">
         <v>13</v>
@@ -6277,23 +6377,23 @@
     </row>
     <row r="179" spans="2:10" ht="15" customHeight="1">
       <c r="B179" s="12" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C179" s="13"/>
       <c r="D179" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E179" s="13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F179" s="14">
-        <v>-471750</v>
+        <v>-74900</v>
       </c>
       <c r="G179" s="15">
-        <v>-3659.84</v>
+        <v>-2587.42</v>
       </c>
       <c r="H179" s="16">
-        <v>-0.002861824508</v>
+        <v>-0.0019087976046</v>
       </c>
       <c r="I179" s="15" t="s">
         <v>13</v>
@@ -6304,23 +6404,23 @@
     </row>
     <row r="180" spans="2:10" ht="15" customHeight="1">
       <c r="B180" s="12" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C180" s="13"/>
       <c r="D180" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E180" s="13" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="F180" s="14">
-        <v>-108325</v>
+        <v>-281250</v>
       </c>
       <c r="G180" s="15">
-        <v>-3800.04</v>
+        <v>-2683.97</v>
       </c>
       <c r="H180" s="16">
-        <v>-0.0029714543814</v>
+        <v>-0.001980024699</v>
       </c>
       <c r="I180" s="15" t="s">
         <v>13</v>
@@ -6331,23 +6431,23 @@
     </row>
     <row r="181" spans="2:10" ht="15" customHeight="1">
       <c r="B181" s="12" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C181" s="13"/>
       <c r="D181" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E181" s="13" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F181" s="14">
-        <v>-4414500</v>
+        <v>-66600</v>
       </c>
       <c r="G181" s="15">
-        <v>-4131.09</v>
+        <v>-2881.78</v>
       </c>
       <c r="H181" s="16">
-        <v>-0.0032303200705</v>
+        <v>-0.0021259535603</v>
       </c>
       <c r="I181" s="15" t="s">
         <v>13</v>
@@ -6358,23 +6458,23 @@
     </row>
     <row r="182" spans="2:10" ht="15" customHeight="1">
       <c r="B182" s="12" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C182" s="13"/>
       <c r="D182" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E182" s="13" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F182" s="14">
-        <v>-598050</v>
+        <v>-150450</v>
       </c>
       <c r="G182" s="15">
-        <v>-5680.88</v>
+        <v>-2956.34</v>
       </c>
       <c r="H182" s="16">
-        <v>-0.004442183705</v>
+        <v>-0.0021809581399</v>
       </c>
       <c r="I182" s="15" t="s">
         <v>13</v>
@@ -6385,23 +6485,23 @@
     </row>
     <row r="183" spans="2:10" ht="15" customHeight="1">
       <c r="B183" s="12" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="C183" s="13"/>
       <c r="D183" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E183" s="13" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F183" s="14">
-        <v>-139350</v>
+        <v>-2880000</v>
       </c>
       <c r="G183" s="15">
-        <v>-6007.38</v>
+        <v>-3066.34</v>
       </c>
       <c r="H183" s="16">
-        <v>-0.0046974915059</v>
+        <v>-0.0022621076002</v>
       </c>
       <c r="I183" s="15" t="s">
         <v>13</v>
@@ -6412,23 +6512,23 @@
     </row>
     <row r="184" spans="2:10" ht="15" customHeight="1">
       <c r="B184" s="12" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C184" s="13"/>
       <c r="D184" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E184" s="13" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="F184" s="14">
-        <v>-2610300</v>
+        <v>-169125</v>
       </c>
       <c r="G184" s="15">
-        <v>-6787.56</v>
+        <v>-3080.61</v>
       </c>
       <c r="H184" s="16">
-        <v>-0.0053075559472</v>
+        <v>-0.0022726348983</v>
       </c>
       <c r="I184" s="15" t="s">
         <v>13</v>
@@ -6439,23 +6539,23 @@
     </row>
     <row r="185" spans="2:10" ht="15" customHeight="1">
       <c r="B185" s="12" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C185" s="13"/>
       <c r="D185" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E185" s="13" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="F185" s="14">
-        <v>-406000</v>
+        <v>-867000</v>
       </c>
       <c r="G185" s="15">
-        <v>-7090.99</v>
+        <v>-3349.65</v>
       </c>
       <c r="H185" s="16">
-        <v>-0.005544824082</v>
+        <v>-0.0024711117237</v>
       </c>
       <c r="I185" s="15" t="s">
         <v>13</v>
@@ -6466,23 +6566,23 @@
     </row>
     <row r="186" spans="2:10" ht="15" customHeight="1">
       <c r="B186" s="12" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C186" s="13"/>
       <c r="D186" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E186" s="13" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="F186" s="14">
-        <v>-1887900</v>
+        <v>-1875300</v>
       </c>
       <c r="G186" s="15">
-        <v>-7495.91</v>
+        <v>-3578.82</v>
       </c>
       <c r="H186" s="16">
-        <v>-0.0058614526722</v>
+        <v>-0.0026401755584</v>
       </c>
       <c r="I186" s="15" t="s">
         <v>13</v>
@@ -6493,23 +6593,23 @@
     </row>
     <row r="187" spans="2:10" ht="15" customHeight="1">
       <c r="B187" s="12" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C187" s="13"/>
       <c r="D187" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E187" s="13" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="F187" s="14">
-        <v>-2514000</v>
+        <v>-108325</v>
       </c>
       <c r="G187" s="15">
-        <v>-7870.08</v>
+        <v>-3868.29</v>
       </c>
       <c r="H187" s="16">
-        <v>-0.006154036194</v>
+        <v>-0.0028537240517</v>
       </c>
       <c r="I187" s="15" t="s">
         <v>13</v>
@@ -6520,23 +6620,23 @@
     </row>
     <row r="188" spans="2:10" ht="15" customHeight="1">
       <c r="B188" s="12" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C188" s="13"/>
       <c r="D188" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E188" s="13" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F188" s="14">
-        <v>-2959200</v>
+        <v>-2720250</v>
       </c>
       <c r="G188" s="15">
-        <v>-8852.45</v>
+        <v>-3885.06</v>
       </c>
       <c r="H188" s="16">
-        <v>-0.0069222038029</v>
+        <v>-0.0028660956558</v>
       </c>
       <c r="I188" s="15" t="s">
         <v>13</v>
@@ -6547,23 +6647,23 @@
     </row>
     <row r="189" spans="2:10" ht="15" customHeight="1">
       <c r="B189" s="12" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C189" s="13"/>
       <c r="D189" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E189" s="13" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="F189" s="14">
-        <v>-100000000</v>
+        <v>-1323000</v>
       </c>
       <c r="G189" s="15">
-        <v>-9070</v>
+        <v>-4234.26</v>
       </c>
       <c r="H189" s="16">
-        <v>-0.0070923177756</v>
+        <v>-0.0031237083061</v>
       </c>
       <c r="I189" s="15" t="s">
         <v>13</v>
@@ -6574,23 +6674,23 @@
     </row>
     <row r="190" spans="2:10" ht="15" customHeight="1">
       <c r="B190" s="12" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C190" s="13"/>
       <c r="D190" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E190" s="13" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F190" s="14">
-        <v>-1058750</v>
+        <v>-86500</v>
       </c>
       <c r="G190" s="15">
-        <v>-10486.39</v>
+        <v>-4784.75</v>
       </c>
       <c r="H190" s="16">
-        <v>-0.0081998688202</v>
+        <v>-0.0035298170914</v>
       </c>
       <c r="I190" s="15" t="s">
         <v>13</v>
@@ -6601,23 +6701,23 @@
     </row>
     <row r="191" spans="2:10" ht="15" customHeight="1">
       <c r="B191" s="12" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="C191" s="13"/>
       <c r="D191" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E191" s="13" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F191" s="14">
-        <v>-562000</v>
+        <v>-44150</v>
       </c>
       <c r="G191" s="15">
-        <v>-10740.66</v>
+        <v>-4973.50</v>
       </c>
       <c r="H191" s="16">
-        <v>-0.0083986961234</v>
+        <v>-0.003669062188</v>
       </c>
       <c r="I191" s="15" t="s">
         <v>13</v>
@@ -6628,23 +6728,23 @@
     </row>
     <row r="192" spans="2:10" ht="15" customHeight="1">
       <c r="B192" s="12" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C192" s="13"/>
       <c r="D192" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E192" s="13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F192" s="14">
-        <v>-281400</v>
+        <v>-4414500</v>
       </c>
       <c r="G192" s="15">
-        <v>-11631.95</v>
+        <v>-5091.24</v>
       </c>
       <c r="H192" s="16">
-        <v>-0.0090956434123</v>
+        <v>-0.0037559216194</v>
       </c>
       <c r="I192" s="15" t="s">
         <v>13</v>
@@ -6655,23 +6755,23 @@
     </row>
     <row r="193" spans="2:10" ht="15" customHeight="1">
       <c r="B193" s="12" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C193" s="13"/>
       <c r="D193" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E193" s="13" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F193" s="14">
-        <v>-712025</v>
+        <v>-598050</v>
       </c>
       <c r="G193" s="15">
-        <v>-11632</v>
+        <v>-5975.12</v>
       </c>
       <c r="H193" s="16">
-        <v>-0.00909568251</v>
+        <v>-0.0044079796644</v>
       </c>
       <c r="I193" s="15" t="s">
         <v>13</v>
@@ -6682,23 +6782,23 @@
     </row>
     <row r="194" spans="2:10" ht="15" customHeight="1">
       <c r="B194" s="12" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C194" s="13"/>
       <c r="D194" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E194" s="13" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="F194" s="14">
-        <v>-105550</v>
+        <v>-2610300</v>
       </c>
       <c r="G194" s="15">
-        <v>-13010.99</v>
+        <v>-6286.12</v>
       </c>
       <c r="H194" s="16">
-        <v>-0.0101739884956</v>
+        <v>-0.0046374113203</v>
       </c>
       <c r="I194" s="15" t="s">
         <v>13</v>
@@ -6709,23 +6809,23 @@
     </row>
     <row r="195" spans="2:10" ht="15" customHeight="1">
       <c r="B195" s="12" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C195" s="13"/>
       <c r="D195" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E195" s="13" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="F195" s="14">
-        <v>-2602800</v>
+        <v>-100000000</v>
       </c>
       <c r="G195" s="15">
-        <v>-13427.85</v>
+        <v>-6940</v>
       </c>
       <c r="H195" s="16">
-        <v>-0.01049995361</v>
+        <v>-0.0051197932211</v>
       </c>
       <c r="I195" s="15" t="s">
         <v>13</v>
@@ -6736,23 +6836,23 @@
     </row>
     <row r="196" spans="2:10" ht="15" customHeight="1">
       <c r="B196" s="12" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C196" s="13"/>
       <c r="D196" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E196" s="13" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="F196" s="14">
-        <v>-1155000</v>
+        <v>-1887900</v>
       </c>
       <c r="G196" s="15">
-        <v>-14523.550000000001</v>
+        <v>-7547.82</v>
       </c>
       <c r="H196" s="16">
-        <v>-0.0113567400033</v>
+        <v>-0.0055681956296</v>
       </c>
       <c r="I196" s="15" t="s">
         <v>13</v>
@@ -6763,23 +6863,23 @@
     </row>
     <row r="197" spans="2:10" ht="15" customHeight="1">
       <c r="B197" s="12" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C197" s="13"/>
       <c r="D197" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E197" s="13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F197" s="14">
-        <v>-1017900</v>
+        <v>-406000</v>
       </c>
       <c r="G197" s="15">
-        <v>-15130.57</v>
+        <v>-8239.36</v>
       </c>
       <c r="H197" s="16">
-        <v>-0.0118314013854</v>
+        <v>-0.0060783601547</v>
       </c>
       <c r="I197" s="15" t="s">
         <v>13</v>
@@ -6790,23 +6890,23 @@
     </row>
     <row r="198" spans="2:10" ht="15" customHeight="1">
       <c r="B198" s="12" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="C198" s="13"/>
       <c r="D198" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E198" s="13" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="F198" s="14">
-        <v>-11412500</v>
+        <v>-2959200</v>
       </c>
       <c r="G198" s="15">
-        <v>-15428.56</v>
+        <v>-8623.11</v>
       </c>
       <c r="H198" s="16">
-        <v>-0.0120644156935</v>
+        <v>-0.0063614611128</v>
       </c>
       <c r="I198" s="15" t="s">
         <v>13</v>
@@ -6817,23 +6917,23 @@
     </row>
     <row r="199" spans="2:10" ht="15" customHeight="1">
       <c r="B199" s="12" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C199" s="13"/>
       <c r="D199" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E199" s="13" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F199" s="14">
-        <v>-437100</v>
+        <v>-657600</v>
       </c>
       <c r="G199" s="15">
-        <v>-15644.90</v>
+        <v>-10316.43</v>
       </c>
       <c r="H199" s="16">
-        <v>-0.0122335835025</v>
+        <v>-0.0076106611498</v>
       </c>
       <c r="I199" s="15" t="s">
         <v>13</v>
@@ -6844,23 +6944,23 @@
     </row>
     <row r="200" spans="2:10" ht="15" customHeight="1">
       <c r="B200" s="12" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C200" s="13"/>
       <c r="D200" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E200" s="13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F200" s="14">
-        <v>-902650</v>
+        <v>-1103750</v>
       </c>
       <c r="G200" s="15">
-        <v>-15664.14</v>
+        <v>-13246.10</v>
       </c>
       <c r="H200" s="16">
-        <v>-0.0122486282868</v>
+        <v>-0.0097719442343</v>
       </c>
       <c r="I200" s="15" t="s">
         <v>13</v>
@@ -6871,23 +6971,23 @@
     </row>
     <row r="201" spans="2:10" ht="15" customHeight="1">
       <c r="B201" s="12" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C201" s="13"/>
       <c r="D201" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E201" s="13" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F201" s="14">
-        <v>-3578800</v>
+        <v>-712025</v>
       </c>
       <c r="G201" s="15">
-        <v>-15854.08</v>
+        <v>-13304.19</v>
       </c>
       <c r="H201" s="16">
-        <v>-0.0123971525248</v>
+        <v>-0.0098147985265</v>
       </c>
       <c r="I201" s="15" t="s">
         <v>13</v>
@@ -6898,23 +6998,23 @@
     </row>
     <row r="202" spans="2:10" ht="15" customHeight="1">
       <c r="B202" s="12" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C202" s="13"/>
       <c r="D202" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E202" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F202" s="14">
-        <v>-891600</v>
+        <v>-815150</v>
       </c>
       <c r="G202" s="15">
-        <v>-16834.30</v>
+        <v>-13421.44</v>
       </c>
       <c r="H202" s="16">
-        <v>-0.0131636389338</v>
+        <v>-0.0099012964739</v>
       </c>
       <c r="I202" s="15" t="s">
         <v>13</v>
@@ -6925,23 +7025,23 @@
     </row>
     <row r="203" spans="2:10" ht="15" customHeight="1">
       <c r="B203" s="12" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C203" s="13"/>
       <c r="D203" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E203" s="13" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F203" s="14">
-        <v>-253750</v>
+        <v>-945000</v>
       </c>
       <c r="G203" s="15">
-        <v>-20124.66</v>
+        <v>-13752.59</v>
       </c>
       <c r="H203" s="16">
-        <v>-0.0157365472818</v>
+        <v>-0.0101455932355</v>
       </c>
       <c r="I203" s="15" t="s">
         <v>13</v>
@@ -6952,23 +7052,23 @@
     </row>
     <row r="204" spans="2:10" ht="15" customHeight="1">
       <c r="B204" s="12" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C204" s="13"/>
       <c r="D204" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E204" s="13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F204" s="14">
-        <v>-827100</v>
+        <v>-1017900</v>
       </c>
       <c r="G204" s="15">
-        <v>-20519.11</v>
+        <v>-15005.88</v>
       </c>
       <c r="H204" s="16">
-        <v>-0.0160449888195</v>
+        <v>-0.0110701732998</v>
       </c>
       <c r="I204" s="15" t="s">
         <v>13</v>
@@ -6979,23 +7079,23 @@
     </row>
     <row r="205" spans="2:10" ht="15" customHeight="1">
       <c r="B205" s="12" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C205" s="13"/>
       <c r="D205" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E205" s="13" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="F205" s="14">
-        <v>-3204300</v>
+        <v>-3578800</v>
       </c>
       <c r="G205" s="15">
-        <v>-20536.36</v>
+        <v>-15633.99</v>
       </c>
       <c r="H205" s="16">
-        <v>-0.0160584775165</v>
+        <v>-0.0115335440952</v>
       </c>
       <c r="I205" s="15" t="s">
         <v>13</v>
@@ -7006,23 +7106,23 @@
     </row>
     <row r="206" spans="2:10" ht="15" customHeight="1">
       <c r="B206" s="12" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C206" s="13"/>
       <c r="D206" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E206" s="13" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F206" s="14">
-        <v>-826000</v>
+        <v>-11709500</v>
       </c>
       <c r="G206" s="15">
-        <v>-24840.71</v>
+        <v>-18957.68</v>
       </c>
       <c r="H206" s="16">
-        <v>-0.0194242788414</v>
+        <v>-0.0139855045463</v>
       </c>
       <c r="I206" s="15" t="s">
         <v>13</v>
@@ -7033,23 +7133,23 @@
     </row>
     <row r="207" spans="2:10" ht="15" customHeight="1">
       <c r="B207" s="12" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="C207" s="13"/>
       <c r="D207" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E207" s="13" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="F207" s="14">
-        <v>-2365600</v>
+        <v>-520800</v>
       </c>
       <c r="G207" s="15">
-        <v>-26084.29</v>
+        <v>-19041.49</v>
       </c>
       <c r="H207" s="16">
-        <v>-0.0203967005106</v>
+        <v>-0.0140473330578</v>
       </c>
       <c r="I207" s="15" t="s">
         <v>13</v>
@@ -7060,23 +7160,23 @@
     </row>
     <row r="208" spans="2:10" ht="15" customHeight="1">
       <c r="B208" s="12" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C208" s="13"/>
       <c r="D208" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E208" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F208" s="14">
-        <v>-4200350</v>
+        <v>-827100</v>
       </c>
       <c r="G208" s="15">
-        <v>-30213.12</v>
+        <v>-19342.56</v>
       </c>
       <c r="H208" s="16">
-        <v>-0.0236252533664</v>
+        <v>-0.0142694391306</v>
       </c>
       <c r="I208" s="15" t="s">
         <v>13</v>
@@ -7087,7 +7187,7 @@
     </row>
     <row r="209" spans="2:10" ht="15" customHeight="1">
       <c r="B209" s="12" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="C209" s="13"/>
       <c r="D209" s="13" t="s">
@@ -7097,13 +7197,13 @@
         <v>35</v>
       </c>
       <c r="F209" s="14">
-        <v>-9577500</v>
+        <v>-758450</v>
       </c>
       <c r="G209" s="15">
-        <v>-31169.97</v>
+        <v>-22670.07</v>
       </c>
       <c r="H209" s="16">
-        <v>-0.0243734655233</v>
+        <v>-0.0167242176812</v>
       </c>
       <c r="I209" s="15" t="s">
         <v>13</v>
@@ -7114,23 +7214,23 @@
     </row>
     <row r="210" spans="2:10" ht="15" customHeight="1">
       <c r="B210" s="12" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C210" s="13"/>
       <c r="D210" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E210" s="13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F210" s="14">
-        <v>-2347100</v>
+        <v>-253750</v>
       </c>
       <c r="G210" s="15">
-        <v>-40951.03</v>
+        <v>-23399.56</v>
       </c>
       <c r="H210" s="16">
-        <v>-0.0320217991179</v>
+        <v>-0.0172623787701</v>
       </c>
       <c r="I210" s="15" t="s">
         <v>13</v>
@@ -7141,7 +7241,7 @@
     </row>
     <row r="211" spans="2:10" ht="15" customHeight="1">
       <c r="B211" s="12" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="C211" s="13"/>
       <c r="D211" s="13" t="s">
@@ -7151,13 +7251,13 @@
         <v>17</v>
       </c>
       <c r="F211" s="14">
-        <v>-4673500</v>
+        <v>-1212000</v>
       </c>
       <c r="G211" s="15">
-        <v>-59355.79</v>
+        <v>-25310.20</v>
       </c>
       <c r="H211" s="16">
-        <v>-0.0464134646641</v>
+        <v>-0.0186719006318</v>
       </c>
       <c r="I211" s="15" t="s">
         <v>13</v>
@@ -7168,80 +7268,223 @@
     </row>
     <row r="212" spans="2:10" ht="15" customHeight="1">
       <c r="B212" s="12" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C212" s="13"/>
       <c r="D212" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E212" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F212" s="14">
+        <v>-3259300</v>
+      </c>
+      <c r="G212" s="15">
+        <v>-25409.50</v>
+      </c>
+      <c r="H212" s="16">
+        <v>-0.0187451564627</v>
+      </c>
+      <c r="I212" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J212" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" ht="15" customHeight="1">
+      <c r="B213" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C213" s="13"/>
+      <c r="D213" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E213" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F213" s="14">
+        <v>-5045400</v>
+      </c>
+      <c r="G213" s="15">
+        <v>-27966.65</v>
+      </c>
+      <c r="H213" s="16">
+        <v>-0.0206316232113</v>
+      </c>
+      <c r="I213" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J213" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" ht="15" customHeight="1">
+      <c r="B214" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C214" s="13"/>
+      <c r="D214" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E214" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F214" s="14">
+        <v>-9004500</v>
+      </c>
+      <c r="G214" s="15">
+        <v>-30223.60</v>
+      </c>
+      <c r="H214" s="16">
+        <v>-0.0222966257056</v>
+      </c>
+      <c r="I214" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J214" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" ht="15" customHeight="1">
+      <c r="B215" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C215" s="13"/>
+      <c r="D215" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E215" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F215" s="14">
+        <v>-4457750</v>
+      </c>
+      <c r="G215" s="15">
+        <v>-31948.69</v>
+      </c>
+      <c r="H215" s="16">
+        <v>-0.0235692631822</v>
+      </c>
+      <c r="I215" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J215" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="2:10" ht="15" customHeight="1">
+      <c r="B216" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C216" s="13"/>
+      <c r="D216" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F216" s="14">
+        <v>-2365600</v>
+      </c>
+      <c r="G216" s="15">
+        <v>-33882.49</v>
+      </c>
+      <c r="H216" s="16">
+        <v>-0.0249958706939</v>
+      </c>
+      <c r="I216" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J216" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" ht="15" customHeight="1">
+      <c r="B217" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="C217" s="13"/>
+      <c r="D217" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E217" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F217" s="14">
+        <v>-2347100</v>
+      </c>
+      <c r="G217" s="15">
+        <v>-39604.97</v>
+      </c>
+      <c r="H217" s="16">
+        <v>-0.0292174721798</v>
+      </c>
+      <c r="I217" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J217" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" ht="15" customHeight="1">
+      <c r="B218" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C218" s="13"/>
+      <c r="D218" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E218" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F212" s="14">
-        <v>-4082100</v>
-      </c>
-      <c r="G212" s="15">
-        <v>-69689.61</v>
-      </c>
-      <c r="H212" s="16">
-        <v>-0.0544940308467</v>
-      </c>
-      <c r="I212" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J212" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="216" spans="2:9" ht="15" customHeight="1">
-      <c r="B216" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="C216" s="23"/>
-      <c r="D216" s="23"/>
-      <c r="E216" s="23"/>
-      <c r="F216" s="23"/>
-      <c r="G216" s="23"/>
-      <c r="H216" s="23"/>
-      <c r="I216" s="23"/>
-    </row>
-    <row r="220" spans="2:9" ht="15" customHeight="1">
-      <c r="B220" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="C220" s="23"/>
-      <c r="D220" s="23"/>
-      <c r="E220" s="23"/>
-      <c r="F220" s="23"/>
-      <c r="G220" s="23"/>
-      <c r="H220" s="23"/>
-      <c r="I220" s="23"/>
-    </row>
-    <row r="221" spans="2:8" ht="15" customHeight="1">
-      <c r="B221" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="C221" s="23"/>
-      <c r="D221" s="23"/>
-      <c r="E221" s="23"/>
-      <c r="F221" s="23"/>
-      <c r="G221" s="23"/>
-      <c r="H221" s="23"/>
-    </row>
-    <row r="222" spans="2:8" ht="15" customHeight="1">
-      <c r="B222" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="C222" s="23"/>
-      <c r="D222" s="23"/>
-      <c r="E222" s="23"/>
-      <c r="F222" s="23"/>
-      <c r="G222" s="23"/>
-      <c r="H222" s="23"/>
-    </row>
-    <row r="223" spans="2:8" ht="15" customHeight="1">
+      <c r="F218" s="14">
+        <v>-4673500</v>
+      </c>
+      <c r="G218" s="15">
+        <v>-66807.68</v>
+      </c>
+      <c r="H218" s="16">
+        <v>-0.0492855197668</v>
+      </c>
+      <c r="I218" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J218" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" ht="15" customHeight="1">
+      <c r="B219" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C219" s="13"/>
+      <c r="D219" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E219" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F219" s="14">
+        <v>-5481300</v>
+      </c>
+      <c r="G219" s="15">
+        <v>-107115.56</v>
+      </c>
+      <c r="H219" s="16">
+        <v>-0.079021544375</v>
+      </c>
+      <c r="I219" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J219" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223" spans="2:9" ht="15" customHeight="1">
       <c r="B223" s="13" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="C223" s="23"/>
       <c r="D223" s="23"/>
@@ -7249,43 +7492,11 @@
       <c r="F223" s="23"/>
       <c r="G223" s="23"/>
       <c r="H223" s="23"/>
-    </row>
-    <row r="224" spans="2:8" ht="15" customHeight="1">
-      <c r="B224" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="C224" s="23"/>
-      <c r="D224" s="23"/>
-      <c r="E224" s="23"/>
-      <c r="F224" s="23"/>
-      <c r="G224" s="23"/>
-      <c r="H224" s="23"/>
-    </row>
-    <row r="225" spans="2:8" ht="15" customHeight="1">
-      <c r="B225" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="C225" s="23"/>
-      <c r="D225" s="23"/>
-      <c r="E225" s="23"/>
-      <c r="F225" s="23"/>
-      <c r="G225" s="23"/>
-      <c r="H225" s="23"/>
-    </row>
-    <row r="226" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B226" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="C226" s="23"/>
-      <c r="D226" s="23"/>
-      <c r="E226" s="23"/>
-      <c r="F226" s="23"/>
-      <c r="G226" s="23"/>
-      <c r="H226" s="23"/>
-    </row>
-    <row r="227" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B227" s="24" t="s">
-        <v>310</v>
+      <c r="I223" s="23"/>
+    </row>
+    <row r="227" spans="2:9" ht="15" customHeight="1">
+      <c r="B227" s="13" t="s">
+        <v>324</v>
       </c>
       <c r="C227" s="23"/>
       <c r="D227" s="23"/>
@@ -7293,10 +7504,11 @@
       <c r="F227" s="23"/>
       <c r="G227" s="23"/>
       <c r="H227" s="23"/>
-    </row>
-    <row r="228" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B228" s="24" t="s">
-        <v>311</v>
+      <c r="I227" s="23"/>
+    </row>
+    <row r="228" spans="2:8" ht="15" customHeight="1">
+      <c r="B228" s="13" t="s">
+        <v>325</v>
       </c>
       <c r="C228" s="23"/>
       <c r="D228" s="23"/>
@@ -7305,47 +7517,124 @@
       <c r="G228" s="23"/>
       <c r="H228" s="23"/>
     </row>
-    <row r="229" spans="2:7" ht="59.25" customHeight="1">
-      <c r="B229" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="C229" s="25"/>
-      <c r="D229" s="25"/>
-      <c r="E229" s="25"/>
-      <c r="F229" s="25"/>
-      <c r="G229" s="25"/>
-    </row>
-    <row r="232" ht="15">
-      <c r="B232" s="23" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="247" ht="15">
-      <c r="B247" s="23" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="248" ht="15">
-      <c r="B248" s="23" t="s">
-        <v>315</v>
+    <row r="229" spans="2:8" ht="15" customHeight="1">
+      <c r="B229" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="C229" s="23"/>
+      <c r="D229" s="23"/>
+      <c r="E229" s="23"/>
+      <c r="F229" s="23"/>
+      <c r="G229" s="23"/>
+      <c r="H229" s="23"/>
+    </row>
+    <row r="230" spans="2:8" ht="15" customHeight="1">
+      <c r="B230" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C230" s="23"/>
+      <c r="D230" s="23"/>
+      <c r="E230" s="23"/>
+      <c r="F230" s="23"/>
+      <c r="G230" s="23"/>
+      <c r="H230" s="23"/>
+    </row>
+    <row r="231" spans="2:8" ht="15" customHeight="1">
+      <c r="B231" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="C231" s="23"/>
+      <c r="D231" s="23"/>
+      <c r="E231" s="23"/>
+      <c r="F231" s="23"/>
+      <c r="G231" s="23"/>
+      <c r="H231" s="23"/>
+    </row>
+    <row r="232" spans="2:8" ht="15" customHeight="1">
+      <c r="B232" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C232" s="23"/>
+      <c r="D232" s="23"/>
+      <c r="E232" s="23"/>
+      <c r="F232" s="23"/>
+      <c r="G232" s="23"/>
+      <c r="H232" s="23"/>
+    </row>
+    <row r="233" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B233" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="C233" s="23"/>
+      <c r="D233" s="23"/>
+      <c r="E233" s="23"/>
+      <c r="F233" s="23"/>
+      <c r="G233" s="23"/>
+      <c r="H233" s="23"/>
+    </row>
+    <row r="234" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B234" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="C234" s="23"/>
+      <c r="D234" s="23"/>
+      <c r="E234" s="23"/>
+      <c r="F234" s="23"/>
+      <c r="G234" s="23"/>
+      <c r="H234" s="23"/>
+    </row>
+    <row r="235" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B235" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="C235" s="23"/>
+      <c r="D235" s="23"/>
+      <c r="E235" s="23"/>
+      <c r="F235" s="23"/>
+      <c r="G235" s="23"/>
+      <c r="H235" s="23"/>
+    </row>
+    <row r="236" spans="2:7" ht="46.5" customHeight="1">
+      <c r="B236" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="C236" s="25"/>
+      <c r="D236" s="25"/>
+      <c r="E236" s="25"/>
+      <c r="F236" s="25"/>
+      <c r="G236" s="25"/>
+    </row>
+    <row r="239" ht="15">
+      <c r="B239" s="23" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="254" ht="15">
+      <c r="B254" s="23" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="255" ht="15">
+      <c r="B255" s="23" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B226:H226"/>
-    <mergeCell ref="B227:H227"/>
+    <mergeCell ref="B233:H233"/>
+    <mergeCell ref="B234:H234"/>
+    <mergeCell ref="B235:H235"/>
+    <mergeCell ref="B236:G236"/>
     <mergeCell ref="B228:H228"/>
-    <mergeCell ref="B229:G229"/>
-    <mergeCell ref="B221:H221"/>
-    <mergeCell ref="B222:H222"/>
-    <mergeCell ref="B223:H223"/>
-    <mergeCell ref="B224:H224"/>
-    <mergeCell ref="B225:H225"/>
+    <mergeCell ref="B229:H229"/>
+    <mergeCell ref="B230:H230"/>
+    <mergeCell ref="B231:H231"/>
+    <mergeCell ref="B232:H232"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B216:I216"/>
-    <mergeCell ref="B220:I220"/>
+    <mergeCell ref="B223:I223"/>
+    <mergeCell ref="B227:I227"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
